--- a/results/cluster_ga/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
@@ -652,19 +652,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.31886727563087</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.04894390778596</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.46744721032037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.31823785616503</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.70904924281432</v>
+        <v>36.03836058893813</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.07844900645434</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.56499768399019</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.09035441945778</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.08152488270041</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.32240695693154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.35037702536806</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.2921382427355</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.98728760895486</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.4476926954361</v>
+        <v>29.06460205994384</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.62070237561744</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.17448905338338</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.59289510562332</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.25777633308993</v>
       </c>
     </row>
   </sheetData>
@@ -784,19 +784,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.56444479292116</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.38293409224742</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.18596094150599</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.33424725542623</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.70322421932898</v>
+        <v>25.24203386708257</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.34800978122134</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.65281662583204</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.03379436498353</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.36470374411783</v>
       </c>
     </row>
   </sheetData>
@@ -850,19 +850,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.11671511222859</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.67609517496167</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.49979792892815</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.60481995293399</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.07123878071549</v>
+        <v>33.65888779631473</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.45314702560898</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.85347978209749</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.97610813604354</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.40868045896428</v>
       </c>
     </row>
   </sheetData>
@@ -916,19 +916,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.72285239674279</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.81340234290689</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.82823750131771</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.20345996704881</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.25114858388134</v>
+        <v>39.66410891786642</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.45518694415477</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.33844824087024</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.05176231429607</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.79585487393125</v>
       </c>
     </row>
   </sheetData>
@@ -982,19 +982,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.66109898045262</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.100036203138</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.80737211415549</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.16797124285458</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.51553983777401</v>
+        <v>37.59781494890383</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.19671818312557</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.82905178499089</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.38125097023095</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.59111937638174</v>
       </c>
     </row>
   </sheetData>
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.85571550751446</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.73456366824817</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.68717681125897</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.52389375553998</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.06820085423109</v>
+        <v>23.54384675033085</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.91830839380944</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.19698977911064</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.76011918677191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.06318332457797</v>
       </c>
     </row>
   </sheetData>
@@ -1114,19 +1114,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.90836790517383</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49.86737050948361</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.37261710305585</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.81272613135898</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.20483308905136</v>
+        <v>29.78075692222163</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.22605350230289</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.70736454573733</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.6593535062712</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.0615711587172</v>
       </c>
     </row>
   </sheetData>
@@ -1180,19 +1180,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.27598893691968</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.80146369479797</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.52156767948631</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.12972017159219</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.06711239219487</v>
+        <v>30.28492370590236</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.38769541048858</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.65697874071008</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.44464566432424</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.57911253972961</v>
       </c>
     </row>
   </sheetData>
@@ -1246,19 +1246,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.96418070947934</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.60394687006763</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.57904402518932</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.18825464242611</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.07720476991605</v>
+        <v>28.40513344743541</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.42406491934936</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.38782639979043</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.14965520920963</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.54927242643251</v>
       </c>
     </row>
   </sheetData>
@@ -1312,19 +1312,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.63080392180174</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.54983554780158</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.17344801083218</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.06792098756348</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.34905654995906</v>
+        <v>26.31881589148015</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.8324867459711</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.54053035283301</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.58360152845196</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.66259899847313</v>
       </c>
     </row>
   </sheetData>
@@ -1378,19 +1378,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.37518138875255</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.88424638330543</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.82307699916108</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.32920680682403</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.81266703756469</v>
+        <v>38.31766129709304</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.98182538316675</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.89333196315089</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.35555952668027</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.9100763154003</v>
       </c>
     </row>
   </sheetData>
@@ -1444,19 +1444,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.71261792769583</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.62862671897646</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.61907677901272</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.37954046934806</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.5909501760548</v>
+        <v>25.26571700078312</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.87401907111355</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.32629057223052</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.86632817924804</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.93983464170782</v>
       </c>
     </row>
   </sheetData>
@@ -1510,19 +1510,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.02935890496421</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.86348867318105</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.94939469637037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.54850410476136</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.47828494848719</v>
+        <v>27.30938136794095</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.03249637219452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.84301479178207</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.4828449293204</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.77265668518812</v>
       </c>
     </row>
   </sheetData>
@@ -1576,19 +1576,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.14886513956392</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.45089662148199</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.3307934059285</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.37935619609298</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.12446290083401</v>
+        <v>26.70462089833519</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.3979766237031</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.03512427969392</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.99189136241636</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.49067968083262</v>
       </c>
     </row>
   </sheetData>
@@ -1642,19 +1642,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.77628728150234</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.49281476017561</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.33644172122718</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.67204440461877</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.20173878948568</v>
+        <v>29.3064790571101</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.34113692611648</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.50915827342489</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.77029585031082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.92237202392069</v>
       </c>
     </row>
   </sheetData>
@@ -1708,19 +1708,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.05439350599985</v>
-      </c>
-      <c r="C2" t="n">
-        <v>55.2431605234644</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.51816438388065</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19.91573246272574</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.99039009570065</v>
+        <v>33.56888218638314</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.31048818496655</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.30914390109011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.12538115056874</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.02931447116485</v>
       </c>
     </row>
   </sheetData>
@@ -1774,19 +1774,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.35075625505994</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.95347007260059</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.7354505557896</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.37727106483959</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.84075300656374</v>
+        <v>19.97161028913306</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.23383858743007</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.62572880444912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.34989886667072</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.32104809183548</v>
       </c>
     </row>
   </sheetData>
@@ -1840,19 +1840,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.33148862405506</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.37067113558897</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.19781806828864</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.9473808330488</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.23014372985852</v>
+        <v>23.423793812982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.41145994744814</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.08469229552528</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.69675987522407</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.59755744398448</v>
       </c>
     </row>
   </sheetData>
@@ -1906,19 +1906,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.14885082096742</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.17118805583637</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15.76307986955161</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.58084231024888</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.08721721170591</v>
+        <v>29.22387017854145</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.52870852558942</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.00180165954048</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.76631063705704</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.30554796151588</v>
       </c>
     </row>
   </sheetData>
@@ -1972,19 +1972,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.06696171610237</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.22340569988607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.49140846194627</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.15426699546459</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.69504720444517</v>
+        <v>25.71545759320967</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.49470275116648</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.80909609499948</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.51145282223455</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.17506277222619</v>
       </c>
     </row>
   </sheetData>
@@ -2038,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.51264928648306</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.84961844193982</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.97458023367144</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.3784785050542</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.0448707916557</v>
+        <v>28.94414081600488</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.27634633421513</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.40896507863044</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.83363040064412</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.77341396534186</v>
       </c>
     </row>
   </sheetData>
@@ -2104,19 +2104,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.50325383588659</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.82175144117127</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.27639445852993</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.55595191033826</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.6700435950437</v>
+        <v>25.6877678005934</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.78123050594041</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.86793086608441</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.50449056992021</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.75710901641779</v>
       </c>
     </row>
   </sheetData>
@@ -2170,19 +2170,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.90407773662034</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.57176256257578</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.94527242189249</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.69800233880058</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.69821812041648</v>
+        <v>30.31087625584323</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.90469815807119</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.65830050210725</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.64572850696941</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.05771215395518</v>
       </c>
     </row>
   </sheetData>
@@ -2236,19 +2236,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.46731757681853</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.8268121330316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.84837166832807</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.63956591121581</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.55741824319137</v>
+        <v>25.45845930135678</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.98799330624967</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.77473918159744</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.04574456340557</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.84123112228361</v>
       </c>
     </row>
   </sheetData>
@@ -2302,19 +2302,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.00151877820694</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.20044071770438</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.60977649660999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.21781520327545</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.02609468735517</v>
+        <v>18.9013589135183</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.74976421610065</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.41229749823015</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.90584635192177</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.63716972086694</v>
       </c>
     </row>
   </sheetData>
@@ -2368,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.98491911397876</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.98303551180452</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.73906740007413</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.98507139220299</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.29167398280815</v>
+        <v>32.98395590317125</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.19745980707733</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.31037119333072</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.72260516477096</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.86630381488823</v>
       </c>
     </row>
   </sheetData>
@@ -2434,19 +2434,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.75622114740765</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.37371836867541</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.28310432380673</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.57663628374701</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.90001240601793</v>
+        <v>32.13397877281177</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.63329678907211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.9075969632068</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.0840917818798</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.37814848706418</v>
       </c>
     </row>
   </sheetData>
@@ -2500,19 +2500,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.45934386607028</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.35952463399029</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.6862108705776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.81485717588895</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.26519094174929</v>
+        <v>24.68608409382632</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.18327939449284</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.21130231310071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.77048321170425</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.79350233294728</v>
       </c>
     </row>
   </sheetData>
@@ -2566,19 +2566,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.317748735083</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.25790190881465</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.80522707519803</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.66660095970971</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.88148108441043</v>
+        <v>36.72109428596604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.55071211633605</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.70801208989484</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.66728955313598</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.42106496369962</v>
       </c>
     </row>
   </sheetData>
@@ -2632,19 +2632,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.64516630334482</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.72469222052527</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.64946634361427</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.65783839729814</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.96320061618783</v>
+        <v>32.50450561916379</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.80047849741233</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.49561282261273</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.37459745346946</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.10885587913317</v>
       </c>
     </row>
   </sheetData>
@@ -2698,19 +2698,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.81413490421045</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.66921725735057</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.93765855658408</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.35749385299523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.53791046256708</v>
+        <v>29.75047746717937</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.45003413292638</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.69760881068721</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.82185103921122</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.25419792069776</v>
       </c>
     </row>
   </sheetData>
@@ -2764,19 +2764,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.51774717451746</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.32219594674247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.1959983000674</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.97910565617342</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.74489245867867</v>
+        <v>27.43540719571428</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.01488030242753</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.44142039302528</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.95695191163276</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.57737727206857</v>
       </c>
     </row>
   </sheetData>
@@ -2830,19 +2830,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.17490288140651</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.50922282290048</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.69906283887379</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.05820591584266</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.79760886847493</v>
+        <v>29.07588047161225</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.85070069364174</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.69833598765425</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.29876303612107</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.6418870387367</v>
       </c>
     </row>
   </sheetData>
@@ -2896,19 +2896,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.25024002062871</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.96392777415574</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.31872111709492</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.05512759105741</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.49848645208291</v>
+        <v>32.77392081239014</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.56319639196418</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.98341849070466</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.76097289022512</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.36679342089241</v>
       </c>
     </row>
   </sheetData>
@@ -2962,19 +2962,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.33574570339664</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.78921644190319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.15790872929404</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.37681368658246</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.24832428221977</v>
+        <v>28.45209820999215</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.37488071582424</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.28251746874967</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.61047325659339</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.02892659646745</v>
       </c>
     </row>
   </sheetData>
@@ -3028,19 +3028,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.20495570867639</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.86099019126509</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.51327883951618</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.68279218899293</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.61460525630534</v>
+        <v>34.06588605925172</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.64424556636373</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.59381797315655</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.4706635126695</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.09452072229897</v>
       </c>
     </row>
   </sheetData>
@@ -3094,19 +3094,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.93886507712848</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.29719375502959</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.04756703946332</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.18501175734652</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.02779392833861</v>
+        <v>26.88148351795763</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.8953754163531</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.36540615856045</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.82146517460109</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.14499195619941</v>
       </c>
     </row>
   </sheetData>
@@ -3160,19 +3160,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.50930893064395</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.17976971561019</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.14822846909786</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.72965599129931</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.76889479483081</v>
+        <v>31.02854660227506</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.76091976857447</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.52333932731652</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.49256594781807</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.63077671720315</v>
       </c>
     </row>
   </sheetData>
@@ -3226,19 +3226,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.93533719305045</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.9994842631031</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.18192112320845</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.88077625842387</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.66128522014972</v>
+        <v>33.11506017091188</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.57980550127615</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.6303339622695</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.79753314888347</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.34608521193997</v>
       </c>
     </row>
   </sheetData>
@@ -3292,19 +3292,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.52584137733433</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.99013582595981</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.45945796268898</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.89751208760097</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.02748267813449</v>
+        <v>34.3031365352388</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.11418164319755</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.83714810792202</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.25341821534396</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.59824520121226</v>
       </c>
     </row>
   </sheetData>
@@ -3358,19 +3358,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.15096140385852</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.8149762930553</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.51011135595529</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.31808886919779</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.5803298262767</v>
+        <v>31.9897966674707</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.04358826981594</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.25365552179493</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.91345502536863</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.82560109368553</v>
       </c>
     </row>
   </sheetData>
@@ -3424,19 +3424,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.09185996114002</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.80820543615304</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.9903976609143</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.78115743779628</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.98630190592117</v>
+        <v>32.97795103241998</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.21229946341934</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.74262782900751</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.8719452086066</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.44528586414399</v>
       </c>
     </row>
   </sheetData>
@@ -3490,19 +3490,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.01168374757119</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.69247054905015</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.85254183543799</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.00143972468227</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.12239694020634</v>
+        <v>30.43883561145603</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.69454178213346</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.43767488842319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.70024727330189</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.13302016536241</v>
       </c>
     </row>
   </sheetData>
@@ -3556,19 +3556,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.32259211128889</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.55768470762316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.46732519316961</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.12634203344809</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.69983024600266</v>
+        <v>24.7142456242178</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.7879353125939</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.51465407092689</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.55082039905465</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.09364618543302</v>
       </c>
     </row>
   </sheetData>
@@ -3622,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.15046349179407</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.54510353962461</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.42453211238661</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.29512786361191</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.23426471754119</v>
+        <v>25.65456148618394</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.45866830461681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.51692823530976</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.33571638369765</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.64152127675587</v>
       </c>
     </row>
   </sheetData>
@@ -3688,19 +3688,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.91212133730101</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.46306910308381</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.53728906208397</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.43462621199701</v>
-      </c>
-      <c r="F2" t="n">
-        <v>56.55209218544297</v>
+        <v>28.80532327317491</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.33116744193154</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.46278711073651</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.02428974027436</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.87108172812531</v>
       </c>
     </row>
   </sheetData>
@@ -3754,19 +3754,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.88105644719986</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.50953431022792</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.60714841662971</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.18456923238767</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.46871118445328</v>
+        <v>24.9539958134668</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.06963314222577</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.0520405369887</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.02420873086194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.17117241978746</v>
       </c>
     </row>
   </sheetData>
@@ -3820,19 +3820,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.32511201335391</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.91666300150128</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.16711210348565</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.30806210488414</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.35731900157275</v>
+        <v>32.32398659071973</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.64341720708966</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.95528057608369</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.84917479766442</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.43846856242745</v>
       </c>
     </row>
   </sheetData>
@@ -3886,19 +3886,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.91146864577234</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.10934738607045</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.70475097760325</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.16035794976271</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.82965267415374</v>
+        <v>28.13843501266197</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.79179124414883</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.82623624271899</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.88832089048758</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.65212053914004</v>
       </c>
     </row>
   </sheetData>
@@ -3952,19 +3952,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.32857546431686</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.90411743002629</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.48379107079703</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.9352913304678</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.00777709763076</v>
+        <v>23.33012599597582</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.22511800037378</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.61960043098138</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.48545719384851</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.82795232327095</v>
       </c>
     </row>
   </sheetData>
@@ -4018,19 +4018,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.39926202645798</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.63374539178681</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.02534318585307</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.56434409707572</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.7268197659142</v>
+        <v>24.25427345439717</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.72134987395661</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.63752009896266</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.33376190186342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.0259680772911</v>
       </c>
     </row>
   </sheetData>
@@ -4084,19 +4084,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.85448384413082</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.953194805985</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.50717214893783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.24948360734504</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.11047687598269</v>
+        <v>25.63821456909435</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.41655817121639</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.64680185140125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.48668215016749</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.49466338849242</v>
       </c>
     </row>
   </sheetData>
@@ -4150,19 +4150,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.58500080906942</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.92932660269564</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.98199599122078</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.65329637410602</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.39302451051649</v>
+        <v>29.86323030914781</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.62628389489569</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.8774684285752</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.25708969846318</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.10107310901604</v>
       </c>
     </row>
   </sheetData>
@@ -4216,19 +4216,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.61555197789438</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.31243510064066</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.68224600847264</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.44242573788159</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.94426438956576</v>
+        <v>28.89051849807233</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.34010386529727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.13151890966546</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.65050568071636</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.18519778483343</v>
       </c>
     </row>
   </sheetData>
@@ -4282,19 +4282,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.35300296627571</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.82444782873976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.07491375119279</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.62741065585436</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.63829545387298</v>
+        <v>27.5066915740157</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.47995540651487</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.60275740493297</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.72682422054784</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.46253991918187</v>
       </c>
     </row>
   </sheetData>
@@ -4348,19 +4348,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.58379540137563</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.18268018634179</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.03374959646228</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.69132974651247</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.37165152854526</v>
+        <v>32.65374772162501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.39352854329111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.17059257317185</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.61582703303149</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.92238726642377</v>
       </c>
     </row>
   </sheetData>
@@ -4414,19 +4414,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.38994239788002</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.03963888689779</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.69663401748652</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.2458104473005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.48438808334937</v>
+        <v>32.00206479308748</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.71769448934754</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.70539816919312</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.39585261993098</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.11183736778192</v>
       </c>
     </row>
   </sheetData>
@@ -4480,19 +4480,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.29620636330381</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.01380352030932</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.93238589385754</v>
-      </c>
-      <c r="E2" t="n">
-        <v>46.22494823250202</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.46307851788586</v>
+        <v>23.83892688662464</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.60840688566696</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.55998919081144</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.49753680950426</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.84487588649575</v>
       </c>
     </row>
   </sheetData>
@@ -4546,19 +4546,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.03808602932251</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.60057415690891</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.73725408240597</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.77460779496037</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.30318289214283</v>
+        <v>36.86149246612003</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.00029744538717</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.95787156736886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.01740225281955</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.77975139166436</v>
       </c>
     </row>
   </sheetData>
@@ -4612,19 +4612,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.35895767018691</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.89101885956915</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.33741162805851</v>
-      </c>
-      <c r="E2" t="n">
-        <v>47.32156073471523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.08409688362252</v>
+        <v>28.95963812710579</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.23106181990177</v>
+      </c>
+      <c r="D2" t="n">
+        <v>43.9673346634751</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.74484551877137</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.05976897146031</v>
       </c>
     </row>
   </sheetData>
@@ -4678,19 +4678,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.81413904357921</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.26807022698129</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.55576738613706</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.42564897491551</v>
-      </c>
-      <c r="F2" t="n">
-        <v>54.16866207457446</v>
+        <v>19.32453427612277</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.81994351038504</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.67404384594707</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.37795057041542</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.31164521447462</v>
       </c>
     </row>
   </sheetData>
@@ -4744,19 +4744,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.92918411145112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.79281390574818</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.50301540631284</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.11497559952351</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.18736246514847</v>
+        <v>21.27586520836632</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.39786968798014</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.84040678736266</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.5360303515892</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.91632378186101</v>
       </c>
     </row>
   </sheetData>
@@ -4810,19 +4810,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.35410692001515</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.13401254347367</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.67913317866129</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.82090036184268</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.89633917582197</v>
+        <v>28.46747169642427</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.54866250283301</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.07373298841658</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.10070423699711</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.78947453249027</v>
       </c>
     </row>
   </sheetData>
@@ -4876,19 +4876,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.01895308527475</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.75932748127604</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.75297348584402</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.97706848631356</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.27332979646998</v>
+        <v>23.12625175527148</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.77851704037919</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.83122590489899</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.77848944728497</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.93437955214639</v>
       </c>
     </row>
   </sheetData>
@@ -4942,19 +4942,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.05457315931453</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.73912274880541</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.97361708818849</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.05903747808969</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.12968635815473</v>
+        <v>26.97526595975084</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.72739181896351</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.56886520284304</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.02270442277507</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.38617908668359</v>
       </c>
     </row>
   </sheetData>
@@ -5008,19 +5008,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.80878837623933</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.93000190421223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.70072160920531</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.28567895854829</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.77712100341494</v>
+        <v>30.00725996424806</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.53819114692693</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.22675047061189</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.69883153076145</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.80098121035824</v>
       </c>
     </row>
   </sheetData>
@@ -5074,19 +5074,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.7787702752514</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.22028227723656</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.33264685775647</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.53624304624089</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.22750412732945</v>
+        <v>31.40218806371194</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.42846456692097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.36118563465521</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.93683608410072</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.29241170262257</v>
       </c>
     </row>
   </sheetData>
@@ -5140,19 +5140,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.11323085360242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.23870112274545</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.83658988566248</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.04318697919422</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.24632018128043</v>
+        <v>26.54097494544634</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.00527905666317</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.76796083898554</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.64926450365468</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.86174353803597</v>
       </c>
     </row>
   </sheetData>
@@ -5206,19 +5206,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.64274119375634</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.30443994233267</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.12502160070801</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.38900789607012</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.70626645724909</v>
+        <v>22.60259790081635</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.80642133871984</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.18413185542339</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.46357340636157</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.83994584523729</v>
       </c>
     </row>
   </sheetData>
@@ -5272,19 +5272,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.33801451209874</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.17607330316309</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.13296392211111</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.90233196054021</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.63262130457056</v>
+        <v>29.74825938012981</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.64266568573341</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.84069993688949</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.33612180659032</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.73339636961993</v>
       </c>
     </row>
   </sheetData>
@@ -5338,19 +5338,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.45825944820872</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.83303104468873</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.5841416924691</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.61330445455742</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.93130444719274</v>
+        <v>28.66496454616384</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.29457940551598</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.72731453232373</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.48588649800081</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.803283211944</v>
       </c>
     </row>
   </sheetData>
@@ -5404,19 +5404,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.36912402855066</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.82927123489531</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.02651772311533</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.16449348565902</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.4802837040312</v>
+        <v>27.05095572054528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.11082449038114</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.34201746028469</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.87879272298212</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.16238341110747</v>
       </c>
     </row>
   </sheetData>
@@ -5470,19 +5470,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.21136931441938</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.75348981725548</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.27228693477491</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.61349648908415</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.43193642599556</v>
+        <v>34.86240284909194</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.63158503354428</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.9116165273413</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.95932164054037</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.04671760676563</v>
       </c>
     </row>
   </sheetData>
@@ -5536,19 +5536,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.77385566930112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.47663444799952</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.28210287993409</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.34735170687698</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.69976922042986</v>
+        <v>31.82623651330645</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.84066281894367</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.82622270006132</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.24011952120172</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.81509114112348</v>
       </c>
     </row>
   </sheetData>
@@ -5602,19 +5602,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23690926984722</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.063315794964</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.78992020974118</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.06009170365059</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.38619192339907</v>
+        <v>40.49992717097561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.24772700670891</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.06374691425964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.59062382551702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.50665997258869</v>
       </c>
     </row>
   </sheetData>
@@ -5668,19 +5668,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.18982902613771</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.73812154475871</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.03682744502051</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.18736063995606</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.21145207391929</v>
+        <v>29.86456990903147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.9619820129722</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.69802156913398</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.88852812649442</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.00529545057674</v>
       </c>
     </row>
   </sheetData>
@@ -5734,19 +5734,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.7482249648267</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.94134365458262</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.41827612312367</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.38003783832826</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.0140263044269</v>
+        <v>28.87419170416372</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.5222072610351</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.98326889558829</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.99892284947193</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.12210139533154</v>
       </c>
     </row>
   </sheetData>
@@ -5800,19 +5800,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.31651504158375</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.12705504660048</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.98962416379736</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.06618787472465</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.28074199282109</v>
+        <v>37.91238903578017</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.63029733725381</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.06983479196468</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.0498403157478</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.29095096318107</v>
       </c>
     </row>
   </sheetData>
@@ -5866,19 +5866,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.13131261745016</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.05266927529408</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.64177280045966</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.08529928457678</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.88490895207486</v>
+        <v>23.0095917659374</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.48880844824018</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.35637364595449</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.24657901799952</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.40509055622242</v>
       </c>
     </row>
   </sheetData>
@@ -5932,19 +5932,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.26494573806092</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.60019840709457</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.49565127489531</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.76093065668261</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.14098825818514</v>
+        <v>27.63521794214221</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.46112727316476</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.58594564376058</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.53655847549951</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.80467627961981</v>
       </c>
     </row>
   </sheetData>
@@ -5998,19 +5998,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.96380912591462</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.13202910370371</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.49469720012365</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.84246533419972</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.03336648676432</v>
+        <v>25.71058617893371</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.62636568970341</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.1094866456695</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.06249042881703</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.59022452418446</v>
       </c>
     </row>
   </sheetData>
@@ -6064,19 +6064,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.20013675905643</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.75154227962452</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.66696328441911</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.63478706391339</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.33347939791705</v>
+        <v>37.38511065707021</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.88361560983336</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.8201321229559</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.9230697533303</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.52318013481413</v>
       </c>
     </row>
   </sheetData>
@@ -6130,19 +6130,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.55926277637414</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.91936424285107</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.52369001830664</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.82892473174753</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.11926521501941</v>
+        <v>27.52507667395884</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.78325244504233</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.93521170569193</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.65008363119774</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.77185947185437</v>
       </c>
     </row>
   </sheetData>
@@ -6196,19 +6196,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.64578589293425</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.40030324575029</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.63402046852998</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.34853954698232</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.98364533041408</v>
+        <v>28.01439984662839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.87416045351132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.79827857515506</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.25382924267624</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.91418652367885</v>
       </c>
     </row>
   </sheetData>
@@ -6262,19 +6262,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.56161727016638</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.79198918898879</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.2926664666229</v>
-      </c>
-      <c r="E2" t="n">
-        <v>18.36615280024201</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.2416116169175</v>
+        <v>29.49708049329933</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.24592232930208</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.42089897822162</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.29054824246715</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.66295203424434</v>
       </c>
     </row>
   </sheetData>
@@ -6328,19 +6328,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.02740058654883</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.94373186973436</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.20932527454465</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.87580721727736</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50.47170005051897</v>
+        <v>19.65091599082793</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.80524732841717</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.65186531507128</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.35162168539258</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.86287420921366</v>
       </c>
     </row>
   </sheetData>
@@ -6394,19 +6394,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.48871831931585</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.45186438706626</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.17064918476472</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.01252064879094</v>
-      </c>
-      <c r="F2" t="n">
-        <v>86.83968281728053</v>
+        <v>32.70640302222657</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.69134030458831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.54612705309136</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.16482311411379</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.50290966181355</v>
       </c>
     </row>
   </sheetData>
@@ -6460,19 +6460,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.12662649344758</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.23733687265266</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.19107961951109</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.65944266455354</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.9455684214826</v>
+        <v>23.45144748047011</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.79851319416689</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.76369949757435</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.17206440275927</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.57126171130674</v>
       </c>
     </row>
   </sheetData>
@@ -6526,19 +6526,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.98770783102904</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.87188875471872</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.35126088311495</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.20081913288447</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.94734449706401</v>
+        <v>32.072794684622</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.16769258898196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.16365306660342</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.55690730901998</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.327398951323</v>
       </c>
     </row>
   </sheetData>
@@ -6592,19 +6592,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.80133376156067</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.53592111107266</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.1830655781265</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.74154698659231</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.32907275399473</v>
+        <v>27.55344528213097</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.72909526611453</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.9055404163374</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.81108210033834</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.3260494949904</v>
       </c>
     </row>
   </sheetData>
@@ -6658,19 +6658,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.95845740713101</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.30210755025152</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.72360772678577</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.45503536307804</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.63681728456076</v>
+        <v>26.30532585604651</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.02774955214106</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.05025893265928</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.0498399390735</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.98350943442679</v>
       </c>
     </row>
   </sheetData>
@@ -6724,19 +6724,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.40383475401155</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.30458098193508</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.01163688516593</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.24278932570999</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.08623815221004</v>
+        <v>30.94537551243512</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.38119147815763</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.87754461058322</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.09382370311103</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.65970563891261</v>
       </c>
     </row>
   </sheetData>
@@ -6790,19 +6790,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.46517051045732</v>
-      </c>
-      <c r="C2" t="n">
-        <v>17.02692345658841</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.0993051565872</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.03374151366199</v>
-      </c>
-      <c r="F2" t="n">
-        <v>55.40948607393074</v>
+        <v>29.68199824648017</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.43113585680446</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.93901388429514</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.11869415998169</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.76500933912944</v>
       </c>
     </row>
   </sheetData>
@@ -6856,19 +6856,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.10435721947852</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.48342052909883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.96309649380547</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.49537174528528</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.98343269094847</v>
+        <v>31.82358642994867</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.83848869113139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.96200826308916</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.88363322542824</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.42766155326397</v>
       </c>
     </row>
   </sheetData>
@@ -6922,19 +6922,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.9853834341227</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.28071198319499</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.6522421168067</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.16619114614632</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.90546750291551</v>
+        <v>26.62442677147841</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.75605234047319</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.98226300510952</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.4585813829216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.8945617818394</v>
       </c>
     </row>
   </sheetData>
@@ -6988,19 +6988,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.46512255092103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.53540759706507</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.57484755415212</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.80524376934844</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.25577736264531</v>
+        <v>28.8958593692256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.64482069342996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.86659255122026</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.37367156361076</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.12108632742987</v>
       </c>
     </row>
   </sheetData>
@@ -7054,19 +7054,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.0296618736459</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.89328754991502</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.73379905769448</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.13225643211491</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.67641120053552</v>
+        <v>32.03726745004368</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.2837230100296</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.73867152536005</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.79771907879474</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.34668086829772</v>
       </c>
     </row>
   </sheetData>
@@ -7120,19 +7120,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.96205391210375</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.34243111876329</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.07989706858093</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.11633696151822</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.55000891205145</v>
+        <v>29.94667004529677</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.41064358174162</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.16011504956241</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.87220837083618</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.55078172089866</v>
       </c>
     </row>
   </sheetData>
@@ -7186,19 +7186,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.69378468711036</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.76139152406337</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.87440826418504</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.16351318528462</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.85425920814297</v>
+        <v>34.70003842144435</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.24758692587123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.89137875219801</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.02961108305082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.1640714162125</v>
       </c>
     </row>
   </sheetData>
@@ -7252,19 +7252,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.87144780273944</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.19024803281776</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.45362160731412</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.33166687145979</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.10758978341546</v>
+        <v>25.26772406001759</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.28242977369681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.09905321365238</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.34625388234475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.00113637989695</v>
       </c>
     </row>
   </sheetData>
@@ -7318,19 +7318,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.59980752796547</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.32553172532003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.31620037422599</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.24855008055217</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.69196409831783</v>
+        <v>26.51364476029456</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48.44071151324598</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.83126739839673</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.05408154724707</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.41138051804216</v>
       </c>
     </row>
   </sheetData>
@@ -7384,19 +7384,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.0035674060796</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.91285661187935</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.64251577339693</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.86644897131087</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.02494661632062</v>
+        <v>27.47156422054519</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.39029014463177</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.14767854414479</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.97847912765328</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.61986342337215</v>
       </c>
     </row>
   </sheetData>
@@ -7450,19 +7450,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.22867402282268</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.12743474032101</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.5994671212847</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.52578066154459</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.6388340090658</v>
+        <v>25.10052078205824</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.91855200879275</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.78829722924151</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.19636958348025</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.71543550353895</v>
       </c>
     </row>
   </sheetData>
@@ -7516,19 +7516,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.64385900385218</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.36280135489252</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.53250879472555</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.44254569606371</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.79854789955967</v>
+        <v>25.66214610069805</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.49600060147367</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.6346678964122</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.07374088561635</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.69330121862025</v>
       </c>
     </row>
   </sheetData>
@@ -7582,19 +7582,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.98552180583458</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.81550494242526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.67786458555796</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.3324115019958</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.26520104687078</v>
+        <v>28.9036256719623</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.0936324933771</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.20929563763544</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.78310728011336</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.82661282937661</v>
       </c>
     </row>
   </sheetData>
@@ -7648,19 +7648,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.12951611005511</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.6653419036243</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.08125143412751</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.45989673729787</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.79980057171754</v>
+        <v>23.39050949314058</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.25271069378542</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.07635479912514</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.33042199250412</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.98043672285542</v>
       </c>
     </row>
   </sheetData>
@@ -7714,19 +7714,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.90495796192761</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.80120026639969</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.77154175600388</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.97651267839035</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.13211639109034</v>
+        <v>27.88313164281465</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.14983762198602</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.02909247775506</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.2436748911371</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.67217491591663</v>
       </c>
     </row>
   </sheetData>
@@ -7780,19 +7780,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.26549915818652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.74486036314804</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.90158022841755</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.90859504185901</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.49215551168353</v>
+        <v>30.21851670721175</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.40753065903419</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.69560285019955</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.81833196239397</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.03000009831921</v>
       </c>
     </row>
   </sheetData>
@@ -7846,19 +7846,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.38019706264553</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.57936640694999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.12834060878951</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.45035654898095</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.7322027766517</v>
+        <v>29.27649478450144</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.61532508628003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.69875857767287</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.63289597483563</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.72327456342768</v>
       </c>
     </row>
   </sheetData>
@@ -7912,19 +7912,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.67095997083124</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.10765019879103</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.92105794783262</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.31346920700769</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.63399303911418</v>
+        <v>26.62676545924424</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.35224998045046</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.51561167975885</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.44706557237917</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.53411777165695</v>
       </c>
     </row>
   </sheetData>
@@ -7978,19 +7978,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.21294049959852</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.67961099011784</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.77821302473402</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.02458554373088</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.83121396119403</v>
+        <v>29.88141831041497</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.42301547752309</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.57741915765828</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.5377730921551</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.03780173980492</v>
       </c>
     </row>
   </sheetData>
@@ -8044,19 +8044,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.7284929054202</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51.08430370026959</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.96203440458703</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.22799239329828</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.87028263439706</v>
+        <v>25.95947089947687</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.11267263401859</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.84865790375054</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.65407996451638</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.77857658365746</v>
       </c>
     </row>
   </sheetData>
@@ -8110,19 +8110,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.83530771362851</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.38333518095708</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.14254942184362</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.45553582988013</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.84375212166628</v>
+        <v>38.68542784177809</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.62788544643958</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.3448499552369</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.37773251837597</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.15511757309883</v>
       </c>
     </row>
   </sheetData>
@@ -8176,19 +8176,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.20488786321395</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.58370565960951</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.60131088344231</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.10267506037634</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.35282673345187</v>
+        <v>25.74383002224712</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.90602304018913</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.2234906222196</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.48879695681524</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.80212412921841</v>
       </c>
     </row>
   </sheetData>
@@ -8242,19 +8242,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15.81694275406342</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.7809779441925</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.20107141718706</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.07100315744079</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.0535465162953</v>
+        <v>27.83835994869803</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.70234010743905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.95359374016155</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.83171239437545</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.03234068924156</v>
       </c>
     </row>
   </sheetData>
@@ -8308,19 +8308,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.67796483287737</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.75486039989831</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.33172036593277</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.16026380625332</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.69978601764765</v>
+        <v>24.88809793048327</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.84923985850769</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.2406797536015</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.79992361471679</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.84152568972863</v>
       </c>
     </row>
   </sheetData>
@@ -8374,19 +8374,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.56836306044672</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.30917334259319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.97402332243014</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.01613375062564</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.2914744026839</v>
+        <v>21.38140663962837</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.10563700798053</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.92504693880479</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.7518399427101</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.64494321272254</v>
       </c>
     </row>
   </sheetData>
@@ -8440,19 +8440,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.93105203134525</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.71156710306938</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.22435016299473</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.57801137937372</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.18165275096931</v>
+        <v>24.98835355872604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.31669005296727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.1551637749799</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.74566758677237</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.91376320356973</v>
       </c>
     </row>
   </sheetData>
@@ -8506,19 +8506,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.80719325169465</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.39225794098735</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.31104123609794</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.82100446661058</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.47550606891607</v>
+        <v>26.38242211157035</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.81781839124585</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.77170076281965</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.18836156053292</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.67921536773778</v>
       </c>
     </row>
   </sheetData>
@@ -8572,19 +8572,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.15577783261443</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.08902223635383</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.37277490030759</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.41573959915049</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.19616219611751</v>
+        <v>32.66589874164701</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.42063026667786</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.81709860957265</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.7840181162231</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.68961940607325</v>
       </c>
     </row>
   </sheetData>
@@ -8638,19 +8638,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.46162121427429</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.26968912402607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.15844672800365</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.57193651579924</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.02159257456329</v>
+        <v>30.95505754732012</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.11226097090587</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.1016401558418</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.0090973028262</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.93625097447877</v>
       </c>
     </row>
   </sheetData>
@@ -8704,19 +8704,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.02883999836217</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.24633015799838</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.40812512824356</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.35773289073345</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.71072766844908</v>
+        <v>21.94520179610299</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.72676256631632</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.89256979116592</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.21273473427143</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.26288226943142</v>
       </c>
     </row>
   </sheetData>
@@ -8770,19 +8770,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.73983344634778</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.84914331759407</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.59542425092258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.35003860345203</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.98797781294612</v>
+        <v>37.04958528465016</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.25201978664446</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.49849277286727</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.75573449376554</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.13921071035283</v>
       </c>
     </row>
   </sheetData>
@@ -8836,19 +8836,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.8266284331908</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.12917572813626</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.08648539292965</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.85411957976356</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.8414954415157</v>
+        <v>38.04318694513761</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.4482362416984</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.33418968648861</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.67366339708724</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.82544009746232</v>
       </c>
     </row>
   </sheetData>
@@ -8902,19 +8902,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.4800358925711</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.20905864223938</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.34973575035102</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.93632000139941</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.02055613479097</v>
+        <v>31.68153644698738</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.82943770289224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.24887859201902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.94473935372954</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.30346969861619</v>
       </c>
     </row>
   </sheetData>
@@ -8968,19 +8968,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.88900277384499</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.0597906311086</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.99606670341969</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.84169614558703</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.00645918057952</v>
+        <v>31.94628836037108</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.25004576744393</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.2991657555467</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.80291736765432</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.53233614170586</v>
       </c>
     </row>
   </sheetData>
@@ -9034,19 +9034,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.80730637885836</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.10584543702788</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.86444978903731</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.75210153744229</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.98731729957367</v>
+        <v>25.51934546717364</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.94943599869169</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.35893994431179</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.86117502189855</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.55183388285794</v>
       </c>
     </row>
   </sheetData>
@@ -9100,19 +9100,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.01081241356167</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.82384280686328</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.08120886075729</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.44167123463718</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.21953534172571</v>
+        <v>31.1197101768955</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.53013282649425</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.08437927546439</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.33241453423206</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.3605213481383</v>
       </c>
     </row>
   </sheetData>
@@ -9166,19 +9166,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.95118296982594</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.32167056468354</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.22757851673867</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.38612392226824</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.87147709589482</v>
+        <v>26.98955608650607</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.07550773435996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.65775896727298</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.52122365557428</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.76784699011561</v>
       </c>
     </row>
   </sheetData>
@@ -9232,19 +9232,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.35123321676297</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.8229559051301</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.5984423833107</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.90535792545528</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.75242077153494</v>
+        <v>28.59420158627666</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.4092735339947</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.14691567721577</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.43221919284426</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.8162892178773</v>
       </c>
     </row>
   </sheetData>
@@ -9298,19 +9298,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.73180226104858</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.79524629646598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.87942653735561</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.29858689203797</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.14055815982376</v>
+        <v>28.96129447025406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.3306650751447</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.14013379211247</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.67507013473929</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.2852519762442</v>
       </c>
     </row>
   </sheetData>
@@ -9364,19 +9364,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.70696529954256</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.4836440879005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.87915306730874</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.9841536378757</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.73759207109806</v>
+        <v>30.67101530917776</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.0080574245945</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.10034399498831</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.59354206058752</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.33714241837593</v>
       </c>
     </row>
   </sheetData>
@@ -9430,19 +9430,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.71973149463074</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.13898151922055</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.16278810635377</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.16545665884939</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.53961912946962</v>
+        <v>27.72609396125646</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.66707532900572</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.11965348299978</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.15536877004054</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.80152865905043</v>
       </c>
     </row>
   </sheetData>
@@ -9496,19 +9496,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.32952944901284</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.42061599653303</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.83837761806522</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.43936326373248</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.68460034706015</v>
+        <v>26.18067178316423</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.19713554271659</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.5236858969096</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.04592133266244</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.74576535585203</v>
       </c>
     </row>
   </sheetData>
@@ -9562,19 +9562,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.40008545019316</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.76008035742184</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.71743348027453</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.75461007503142</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.0675315965294</v>
+        <v>26.87941043693862</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.34939520432944</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.88844471600162</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.28455508107161</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.51816937427346</v>
       </c>
     </row>
   </sheetData>
@@ -9628,19 +9628,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.83198508882834</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.06018230287344</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.22929262915161</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.99606187121178</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.28468377441575</v>
+        <v>25.84283843520728</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.32483212994746</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.73141678642322</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.16192690327117</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.59627209491778</v>
       </c>
     </row>
   </sheetData>
@@ -9694,19 +9694,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.2754772125488</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.05836715956374</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.48206935143159</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.75531182633157</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.22728140474273</v>
+        <v>25.17420428351965</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.71995622281027</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.18147871441527</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.86778122573964</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.8116113175853</v>
       </c>
     </row>
   </sheetData>
@@ -9760,19 +9760,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.64015217129772</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.9098467347456</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.45669965144023</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.60293219264808</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.50961823463301</v>
+        <v>26.92737908100786</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.01357611526986</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.48166858310153</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.8440230133708</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.73905876427489</v>
       </c>
     </row>
   </sheetData>
@@ -9826,19 +9826,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.41684583633486</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.88776292965939</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.69497377938016</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.12421421784384</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.14583618587411</v>
+        <v>36.00871140239669</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.53646715245949</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.07306849294783</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.09854496906276</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.43635727377253</v>
       </c>
     </row>
   </sheetData>
@@ -9892,19 +9892,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.07298920962893</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.71782388226043</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.38055647727309</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.61397738295447</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.91705618145582</v>
+        <v>34.47473649604268</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.17634390544414</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.10626170131463</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.59759186989402</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.62656487056228</v>
       </c>
     </row>
   </sheetData>
@@ -9958,19 +9958,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.61660678499256</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.33194789060669</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.2656144330666</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.5692210181386</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.64086574036357</v>
+        <v>26.7454136549006</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.20424233802201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.3258349827237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.33202335813059</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.22839854930796</v>
       </c>
     </row>
   </sheetData>
@@ -10024,19 +10024,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.19679289823489</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.09305507886409</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.13127212467067</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.81054922823125</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.85670589508875</v>
+        <v>19.05377258551948</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.25638625050119</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.1794549524295</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.82201787033025</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.55377932813228</v>
       </c>
     </row>
   </sheetData>
@@ -10090,19 +10090,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.41184701420097</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.5538223499201</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.12845192353338</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.63526347631205</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.85905431580654</v>
+        <v>27.95555560866153</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.6934548423657</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.20106454023748</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.56482324284314</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.00102362023964</v>
       </c>
     </row>
   </sheetData>
@@ -10156,19 +10156,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.2565963809175</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.96156049948384</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.99480699932398</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.98070045264853</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.25917294809977</v>
+        <v>29.25170072533952</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.87819747669715</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.56265836911135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.04240112088581</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.2947623360575</v>
       </c>
     </row>
   </sheetData>
@@ -10222,19 +10222,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.92249653430467</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.99211061884751</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.28586236052031</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.39323673009589</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.63303803542676</v>
+        <v>26.76403081015703</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.83933346683344</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.29144088464253</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.87264604398689</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.80181515245083</v>
       </c>
     </row>
   </sheetData>
@@ -10288,19 +10288,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.05593320107135</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.56056416109788</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.91988172140045</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.32459500008965</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.74440089842141</v>
+        <v>29.48045539077151</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.27002707035863</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.15130444747443</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.27856390641532</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.95907394507142</v>
       </c>
     </row>
   </sheetData>
@@ -10354,19 +10354,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.37161478351977</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.47784665665906</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.80580516175954</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.54762021058825</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.75241368607162</v>
+        <v>24.93430570099249</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.54220253272778</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.77280961026307</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.27991930112793</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.77549085175819</v>
       </c>
     </row>
   </sheetData>
@@ -10420,19 +10420,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.02687439553169</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.43525788833936</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.02525272739003</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.96178796313209</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.40609981432235</v>
+        <v>34.66031443232461</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.44339070103882</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.66002942026575</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.02309769472518</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.70989518807076</v>
       </c>
     </row>
   </sheetData>
@@ -10486,19 +10486,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.56489258784245</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.28870724007453</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.456209384636</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.42978319441632</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.0741346014916</v>
+        <v>26.86424651497875</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.33181638550843</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.70548382099436</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.24457620868379</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.17284381300847</v>
       </c>
     </row>
   </sheetData>
@@ -10552,19 +10552,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.97965515142073</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.71015591419747</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.22193253002725</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.33139368403587</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.84187928621366</v>
+        <v>29.12171472482889</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.49426002416989</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.94765106815098</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.33770825541466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.2187152857272</v>
       </c>
     </row>
   </sheetData>
@@ -10618,19 +10618,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.64577042758848</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11.74683899583393</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.74896341384989</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.4023475557883</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.41567808566656</v>
+        <v>23.65258290390334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.11668440374221</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.87074741773534</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.14265481779613</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.69677293804516</v>
       </c>
     </row>
   </sheetData>
@@ -10684,19 +10684,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.57127132032565</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.23687512363528</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.99210347223428</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.78942927901807</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.05979574538328</v>
+        <v>33.94187672089451</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.49263311590188</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.38319194016542</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.43578007176197</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.34377627433453</v>
       </c>
     </row>
   </sheetData>
@@ -10750,19 +10750,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.05495455559656</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.66618188652841</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.98951627311358</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.45598062956419</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.01734471826985</v>
+        <v>31.79672684546412</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.99601023895871</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.20703998723747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.78460701754653</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.51845654850944</v>
       </c>
     </row>
   </sheetData>
@@ -10816,19 +10816,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.1604738165792</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.93799664763581</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.70511015701685</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.76737651804424</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.37877851946816</v>
+        <v>35.52683180998303</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.11960804972414</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.56887323365008</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.39494107893316</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.5122396408343</v>
       </c>
     </row>
   </sheetData>
@@ -10882,19 +10882,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.69611209072865</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50.46753159351846</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.09310541389149</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.55044649930878</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.53343344593711</v>
+        <v>31.75166015993333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.49473049825345</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.92256123716979</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.69448756041159</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.78951848728192</v>
       </c>
     </row>
   </sheetData>
@@ -10948,19 +10948,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.18025127902945</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.37708546757683</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.71270769829672</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.00378968571354</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.41019432592952</v>
+        <v>32.57263724666275</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.53848010558598</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.73933313770748</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.16230783646844</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.98856023897655</v>
       </c>
     </row>
   </sheetData>
@@ -11014,19 +11014,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.46960336678153</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.13158963090175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.47066113982627</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.26173631575836</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.939897723445</v>
+        <v>27.94192454224867</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.30219135137247</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.44638217433681</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.49347075151941</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.39057795369924</v>
       </c>
     </row>
   </sheetData>
@@ -11080,19 +11080,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.92841997475499</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.16350981859278</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.15784670278984</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.60038212990356</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.35472669293323</v>
+        <v>36.01389592745106</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.33659329175341</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.37922049512445</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.79566937822612</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.53633518891028</v>
       </c>
     </row>
   </sheetData>
@@ -11146,19 +11146,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.37860750940997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.32633096346967</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.96378634485718</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.72049256226781</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.3277326381488</v>
+        <v>22.87384467054859</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.98155242717306</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.42987056155772</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.40819743775996</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.1044972679509</v>
       </c>
     </row>
   </sheetData>
@@ -11212,19 +11212,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.39808894218359</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.10691761840847</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.81278097910295</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.87259346466238</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.02153590732651</v>
+        <v>24.26387866830468</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.53008340936613</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.51161742703863</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.2599144719084</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.87731235417368</v>
       </c>
     </row>
   </sheetData>
@@ -11278,19 +11278,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.96875300540473</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.81200803504359</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.47197926023948</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.67426517608608</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51.63860179609406</v>
+        <v>26.44206086679669</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.27799601440021</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.52378147980352</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.85044352144461</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.76695045577598</v>
       </c>
     </row>
   </sheetData>
@@ -11344,19 +11344,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.13129758047741</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.64939945603775</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.33704077766846</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.17514626177465</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.29711530700227</v>
+        <v>24.2168152535969</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.24845167528348</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.02546300273507</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.69435480003517</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.68953983330308</v>
       </c>
     </row>
   </sheetData>
@@ -11410,19 +11410,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.66509163303301</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.75962916830117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.01103099509318</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.52455507150633</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.72718745328559</v>
+        <v>31.37843277122349</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.48331275807935</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.72182020029796</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.96372744716541</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.01938632895901</v>
       </c>
     </row>
   </sheetData>
@@ -11476,19 +11476,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.01928953096449</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.40749694955079</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.82092372798811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.10373120987265</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.86924611202293</v>
+        <v>28.50357779445359</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.34391359590963</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.26024420750376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.56882357053047</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.37717413338052</v>
       </c>
     </row>
   </sheetData>
@@ -11542,19 +11542,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.00469563967081</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.91414862293089</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.27131143590742</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.73497124667289</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.16528794233464</v>
+        <v>28.72660782534061</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.86394277418993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.00728484499826</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.36833281734646</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.83202645437546</v>
       </c>
     </row>
   </sheetData>
@@ -11608,19 +11608,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.41861126591304</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.1549147180766</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.10266520768135</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.33649878918644</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.11223571283422</v>
+        <v>26.54357863834942</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.16595160302063</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.18149014446881</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.38378302683818</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.97079619563879</v>
       </c>
     </row>
   </sheetData>
@@ -11674,19 +11674,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.63942117346451</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.63893336068825</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.11289293437726</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.51614670451486</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.2587962810805</v>
+        <v>26.52649199586127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.59348637255855</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.39063120963664</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.9362700273616</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.12699550247288</v>
       </c>
     </row>
   </sheetData>
@@ -11740,19 +11740,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.68564064044672</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.66630914783832</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.26015400631552</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.48640967897033</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.38640719672022</v>
+        <v>28.14454878815928</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.49987203895307</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.08409353749072</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.95703265054077</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.83887039801733</v>
       </c>
     </row>
   </sheetData>
@@ -11806,19 +11806,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.8837885548413</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.09997152494993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.15004998571882</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.1738063317376</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.36734359692543</v>
+        <v>20.64481120751972</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.48959375768417</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.58850780574831</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.94734677415636</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.59726973515419</v>
       </c>
     </row>
   </sheetData>
@@ -11872,19 +11872,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.05967160189557</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.04784530284407</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.79310004031199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.85377376841207</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.81363582620251</v>
+        <v>24.60651330084773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.37178986527647</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.41660234199644</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.94041594954818</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.60718228028391</v>
       </c>
     </row>
   </sheetData>
@@ -11938,19 +11938,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.51471455010673</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.9636612584228</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.38103967363777</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.75228430170249</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.37915887113218</v>
+        <v>30.39255120116967</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.82034842764735</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.59064323713379</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.2126817776622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.51083065153849</v>
       </c>
     </row>
   </sheetData>
@@ -12004,19 +12004,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.31138379041633</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.69002784549794</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.67067311066483</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.9619725192196</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.53177058080292</v>
+        <v>31.107261905713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.82719896196611</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.70176161363161</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.3306795679367</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.62469541662145</v>
       </c>
     </row>
   </sheetData>
@@ -12070,19 +12070,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.56351404349681</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.47863062395891</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.82324195683277</v>
-      </c>
-      <c r="E2" t="n">
-        <v>43.3840031895343</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.06511516128506</v>
+        <v>21.64893413096174</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.56889269524778</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.273376717306</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.86858181965827</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.55130128082138</v>
       </c>
     </row>
   </sheetData>
@@ -12136,19 +12136,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.72805224091329</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.78676048351092</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.62530534628334</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.92206315671614</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.45273245484245</v>
+        <v>29.34051041544591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.2646716503068</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.02845163407894</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.1360912499329</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.34778250364552</v>
       </c>
     </row>
   </sheetData>
@@ -12202,19 +12202,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.42792179281852</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.01650665608265</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.33289883031158</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.94904580721406</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.14232870961762</v>
+        <v>27.52335792514109</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.27340927021788</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.06976089079097</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.92942348043138</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.92696875928641</v>
       </c>
     </row>
   </sheetData>
@@ -12268,19 +12268,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.45268360903992</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.80823010905979</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.70464700128961</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.32863723115577</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.94137697557007</v>
+        <v>28.4911981568531</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.45433931853248</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.819861153326</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.35175960127386</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.41519596762301</v>
       </c>
     </row>
   </sheetData>
@@ -12334,19 +12334,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.59343036387968</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.78016655789388</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.87070770814479</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.71311245215251</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.60563699778286</v>
+        <v>25.62677624311745</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.08743230692435</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.86582295214392</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.18988274708915</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.99587627049451</v>
       </c>
     </row>
   </sheetData>
@@ -12400,19 +12400,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.80039227390689</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.64183594725997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.1870749639571</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.46798906972648</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.29553962446963</v>
+        <v>24.36887944073847</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.7395384532759</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.52261226282479</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.03931546251395</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.64781282902238</v>
       </c>
     </row>
   </sheetData>
@@ -12466,19 +12466,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.14079432927897</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.44684084586925</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.80762734102247</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.1194077844013</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.81411109956754</v>
+        <v>31.35341419951138</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.97840503172016</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.62282671642852</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.15345556048936</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.25804392855428</v>
       </c>
     </row>
   </sheetData>
@@ -12532,19 +12532,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.08528775656669</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.69175967818669</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.14350849697108</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.81231749265807</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.88535191176525</v>
+        <v>35.99698887424793</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.31611412042138</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.27570360753173</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.03518831350998</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.51041553871115</v>
       </c>
     </row>
   </sheetData>
@@ -12598,19 +12598,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.03409649173112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.83816389724643</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.90459823681219</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.52530864435874</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.76265080641365</v>
+        <v>23.66547701994264</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.42091376811975</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.88063865587248</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.64308211727305</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.00725429991738</v>
       </c>
     </row>
   </sheetData>
@@ -12664,19 +12664,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.34787047906706</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.22652816981572</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.33165044633976</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.60168803122478</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.72828720622139</v>
+        <v>29.90886344332038</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.66580614128953</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.09283886574531</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.05781841582078</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.49383259429552</v>
       </c>
     </row>
   </sheetData>
@@ -12730,19 +12730,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.81819901845425</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.28650799809143</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.53911432673244</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.18619686417731</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.82993832259032</v>
+        <v>25.93467869694505</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.16821952866997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.10344518419397</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.77954476100714</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.29862218515577</v>
       </c>
     </row>
   </sheetData>
@@ -12796,19 +12796,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.14483358995921</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.010924470325</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.29024743017832</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.27051718651531</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.14134102638935</v>
+        <v>31.24663918891241</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.66606768981803</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.75111541327037</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.0935155409019</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.2942834277054</v>
       </c>
     </row>
   </sheetData>
@@ -12862,19 +12862,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.14129830705032</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.83116899399537</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.54187169622024</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.82881143539825</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.85884362351594</v>
+        <v>26.68641477923077</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.44384426415492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.44889913177356</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.26921519507277</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.26583818904382</v>
       </c>
     </row>
   </sheetData>
@@ -12928,19 +12928,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.09646911246444</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.14805474921996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.23647566381624</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.204917337998</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.06390017609392</v>
+        <v>30.03871232971213</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.69352639281366</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.48186607466996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.45529103684427</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.0304049345624</v>
       </c>
     </row>
   </sheetData>
@@ -12994,19 +12994,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.77612884801118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.67183321817537</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.00584665548768</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.55583572617766</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.57922886593254</v>
+        <v>37.52788236218782</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.45360420106156</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.18158167078733</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.34502436463789</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.16440319745509</v>
       </c>
     </row>
   </sheetData>
@@ -13060,19 +13060,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.51030473898459</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.907208158397</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.68407608005542</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.75189812458443</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.94807271165429</v>
+        <v>34.44746962566384</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.57755032127218</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.92799028266214</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.92236026619199</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.77310946392198</v>
       </c>
     </row>
   </sheetData>
@@ -13126,19 +13126,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.61348495997085</v>
-      </c>
-      <c r="C2" t="n">
-        <v>47.05619314390314</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.9891508302347</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.85288126324523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.61901136471813</v>
+        <v>28.48193410214588</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.83124489527661</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.79361735491836</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.95112503003885</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.21373926803165</v>
       </c>
     </row>
   </sheetData>
@@ -13192,19 +13192,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.3689337855679</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.46287645132186</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.98097787672108</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.77948077801092</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.79995904444816</v>
+        <v>25.70712846140271</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.9112037410443</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.7108871126932</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.21653386628595</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.63241103028308</v>
       </c>
     </row>
   </sheetData>
@@ -13258,19 +13258,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.32934683089813</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.6994219714324</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.65442211230605</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.15028926326912</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.57676081045019</v>
+        <v>39.43123933499658</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.97740325045025</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.11755627773092</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.96473404635786</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.51142787611301</v>
       </c>
     </row>
   </sheetData>
@@ -13324,19 +13324,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.46002927822177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.78834119497639</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.13441904591124</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.71664822187237</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.90199204241059</v>
+        <v>29.43953736479984</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.1225065238454</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.88549432167813</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.36723237089722</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.27287927400152</v>
       </c>
     </row>
   </sheetData>
@@ -13390,19 +13390,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.49105391478723</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.47934890562857</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.03742511491797</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.60825075115366</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.579711388142</v>
+        <v>25.5487650689582</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.71852393551812</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.63632831371912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.41216761037523</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.82011549638439</v>
       </c>
     </row>
   </sheetData>
@@ -13456,19 +13456,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.04944749494505</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.26287370148961</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.32513746293429</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.549687721353</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.56489141107618</v>
+        <v>26.87234720423249</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.99287953721651</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.6915232520741</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.88897435383742</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.80159346853944</v>
       </c>
     </row>
   </sheetData>
@@ -13522,19 +13522,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.33855070419571</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.515272625607</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.5726631832071</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.5131873485827</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.37222717733139</v>
+        <v>33.34247755228782</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.49712534016155</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.34611466667748</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.62738591379949</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.49821781143044</v>
       </c>
     </row>
   </sheetData>
@@ -13588,19 +13588,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.24473226814017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.22027498837153</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.49150106976807</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.56352936872101</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.95494629539242</v>
+        <v>42.26926733412599</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.71979575815134</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.5851072762611</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.47284834792412</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.07617452602943</v>
       </c>
     </row>
   </sheetData>
@@ -13654,19 +13654,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.52906420305013</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.03887116058973</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.83202566108846</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.72450521312684</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.63202172816095</v>
+        <v>29.20709302831548</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.7508166790337</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.07515865875312</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.79053917179296</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.69558079067473</v>
       </c>
     </row>
   </sheetData>
@@ -13720,19 +13720,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.44224889637912</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.94851470392458</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.02225703311609</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.32536948512046</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.08987358934505</v>
+        <v>25.21249128420522</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.39750380749179</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.83472364861987</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.10510696438019</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.11160936180518</v>
       </c>
     </row>
   </sheetData>
@@ -13786,19 +13786,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.31703609062099</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.33721150244546</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.29562228430431</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.73368620918819</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.84410075425468</v>
+        <v>31.97546198069178</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.69108506056397</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.96305979986611</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.90166841706135</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.12295906260695</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs5_GRID13/revenue/UAVs5_GRID13_Greedy.xlsx
@@ -652,19 +652,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.03836058893813</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.07844900645434</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.56499768399019</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.09035441945778</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.08152488270041</v>
+        <v>26.86585265543216</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.37379286824758</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.11562781077433</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.89567801901295</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.87221289734621</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.06460205994384</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.62070237561744</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.17448905338338</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.59289510562332</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.25777633308993</v>
+        <v>29.84507527828542</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.94265000387217</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.54960186350098</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.77119080951794</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.38987634772312</v>
       </c>
     </row>
   </sheetData>
@@ -784,19 +784,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.24203386708257</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.34800978122134</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.65281662583204</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.03379436498353</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.36470374411783</v>
+        <v>28.11173623438588</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.27072159630938</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.62333482087629</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.16020277628105</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.88717356702224</v>
       </c>
     </row>
   </sheetData>
@@ -850,19 +850,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.65888779631473</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.45314702560898</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.85347978209749</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.97610813604354</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.40868045896428</v>
+        <v>27.76280376812377</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.29076339749979</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.43659012592849</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.82379683564806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47.22025178541924</v>
       </c>
     </row>
   </sheetData>
@@ -916,19 +916,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.66410891786642</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.45518694415477</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.33844824087024</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.05176231429607</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.79585487393125</v>
+        <v>27.60097743375628</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.87076076775292</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.77325865626396</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.90871404910909</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.27870498870969</v>
       </c>
     </row>
   </sheetData>
@@ -982,19 +982,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.59781494890383</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.19671818312557</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.82905178499089</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.38125097023095</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.59111937638174</v>
+        <v>36.1589711652761</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.25955491848678</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.86221837971976</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.25624169016249</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.99671528784644</v>
       </c>
     </row>
   </sheetData>
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.54384675033085</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.91830839380944</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.19698977911064</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.76011918677191</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.06318332457797</v>
+        <v>25.42651327317975</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.35848189239342</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.21801917706383</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.03694694372325</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.41550753645561</v>
       </c>
     </row>
   </sheetData>
@@ -1114,19 +1114,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.78075692222163</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.22605350230289</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.70736454573733</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.6593535062712</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.0615711587172</v>
+        <v>34.08315686372639</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.28478404667372</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.77401573267568</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.97343372074353</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.50674353584643</v>
       </c>
     </row>
   </sheetData>
@@ -1180,19 +1180,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.28492370590236</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.38769541048858</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.65697874071008</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.44464566432424</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.57911253972961</v>
+        <v>32.97855393859714</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.7367834041921</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.69539462946943</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.14211586444074</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.61557611299945</v>
       </c>
     </row>
   </sheetData>
@@ -1246,19 +1246,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.40513344743541</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.42406491934936</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.38782639979043</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.14965520920963</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.54927242643251</v>
+        <v>30.43949915167889</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.10128988518311</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.10866945627385</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.71809803409766</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.38017117369463</v>
       </c>
     </row>
   </sheetData>
@@ -1312,19 +1312,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.31881589148015</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.8324867459711</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.54053035283301</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.58360152845196</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.66259899847313</v>
+        <v>24.2653655233642</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.06052924674986</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.27370507507489</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.91905916461612</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.53527669684381</v>
       </c>
     </row>
   </sheetData>
@@ -1378,19 +1378,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.31766129709304</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.98182538316675</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.89333196315089</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.35555952668027</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.9100763154003</v>
+        <v>27.03502993652043</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.85896841801678</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.99731891908258</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.02010437172331</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.91838527962388</v>
       </c>
     </row>
   </sheetData>
@@ -1444,19 +1444,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.26571700078312</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.87401907111355</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.32629057223052</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.86632817924804</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.93983464170782</v>
+        <v>27.58527595845305</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.76887653198747</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.50460712681874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.74628646387128</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.5314522609382</v>
       </c>
     </row>
   </sheetData>
@@ -1510,19 +1510,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.30938136794095</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.03249637219452</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.84301479178207</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.4828449293204</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.77265668518812</v>
+        <v>30.88198031274425</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.69841765518117</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.52907353543457</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.12859450852132</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.99862833475413</v>
       </c>
     </row>
   </sheetData>
@@ -1576,19 +1576,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.70462089833519</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.3979766237031</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.03512427969392</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.99189136241636</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.49067968083262</v>
+        <v>27.26163802301471</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.35174315302488</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.07423160078658</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.56980918282935</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.56599466795461</v>
       </c>
     </row>
   </sheetData>
@@ -1642,19 +1642,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.3064790571101</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.34113692611648</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.50915827342489</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.77029585031082</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.92237202392069</v>
+        <v>37.47607627307895</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.17351109568733</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45.83422337755677</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.05777214080253</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.22774046945855</v>
       </c>
     </row>
   </sheetData>
@@ -1708,19 +1708,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.56888218638314</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.31048818496655</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.30914390109011</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.12538115056874</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.02931447116485</v>
+        <v>48.1768206610658</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.55710991052256</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.79189354947978</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.83408464172781</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.72376535889082</v>
       </c>
     </row>
   </sheetData>
@@ -1774,19 +1774,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.97161028913306</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.23383858743007</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.62572880444912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.34989886667072</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.32104809183548</v>
+        <v>25.85194320787516</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.22974182634427</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.32186014721027</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.11506769273216</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.01402776899196</v>
       </c>
     </row>
   </sheetData>
@@ -1840,19 +1840,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.423793812982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.41145994744814</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.08469229552528</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.69675987522407</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.59755744398448</v>
+        <v>31.43141329654484</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.54394457871341</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.43953129624011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.83089999279066</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.00424159308481</v>
       </c>
     </row>
   </sheetData>
@@ -1906,19 +1906,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.22387017854145</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.52870852558942</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.00180165954048</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.76631063705704</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.30554796151588</v>
+        <v>28.2971355323283</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.71173350084243</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.02810250968428</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.73695810032858</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.51010275787979</v>
       </c>
     </row>
   </sheetData>
@@ -1972,19 +1972,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.71545759320967</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.49470275116648</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.80909609499948</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.51145282223455</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46.17506277222619</v>
+        <v>35.90578348980743</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.62736681230586</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.50257263013745</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.80021813043039</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.68876771831722</v>
       </c>
     </row>
   </sheetData>
@@ -2038,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.94414081600488</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.27634633421513</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.40896507863044</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.83363040064412</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.77341396534186</v>
+        <v>41.08610135644251</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.97989223286777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.41407657224644</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.56583637064132</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.34827338610927</v>
       </c>
     </row>
   </sheetData>
@@ -2104,19 +2104,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.6877678005934</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.78123050594041</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.86793086608441</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.50449056992021</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.75710901641779</v>
+        <v>33.32792222934502</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.46483904509727</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.6173083155685</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.83858595130598</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.48814168865408</v>
       </c>
     </row>
   </sheetData>
@@ -2170,19 +2170,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.31087625584323</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.90469815807119</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.65830050210725</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.64572850696941</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.05771215395518</v>
+        <v>29.65539488858482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.58721799675914</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.96633664866261</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.33115209667128</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.19196213164909</v>
       </c>
     </row>
   </sheetData>
@@ -2236,19 +2236,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.45845930135678</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.98799330624967</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.77473918159744</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.04574456340557</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.84123112228361</v>
+        <v>27.816975430805</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.58553933396687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.72423716797717</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.0024685753664</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.06900504247057</v>
       </c>
     </row>
   </sheetData>
@@ -2302,19 +2302,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.9013589135183</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.74976421610065</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.41229749823015</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.90584635192177</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.63716972086694</v>
+        <v>28.9666395342694</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.06238012894114</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.51815301548161</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.15748635810165</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.39471004409249</v>
       </c>
     </row>
   </sheetData>
@@ -2368,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.98395590317125</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.19745980707733</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.31037119333072</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.72260516477096</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.86630381488823</v>
+        <v>33.94186545817143</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.83447898405726</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.53133786878376</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45.96544322007827</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.07650984493378</v>
       </c>
     </row>
   </sheetData>
@@ -2434,19 +2434,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.13397877281177</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.63329678907211</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.9075969632068</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.0840917818798</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.37814848706418</v>
+        <v>34.28089170476522</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.70014833636981</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.21314231463143</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.71563019146842</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.892126713503</v>
       </c>
     </row>
   </sheetData>
@@ -2500,19 +2500,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.68608409382632</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.18327939449284</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.21130231310071</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.77048321170425</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.79350233294728</v>
+        <v>35.66214885329052</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.36987722397898</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.8179958181157</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.20735412277731</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.81242096414369</v>
       </c>
     </row>
   </sheetData>
@@ -2566,19 +2566,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.72109428596604</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.55071211633605</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.70801208989484</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.66728955313598</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.42106496369962</v>
+        <v>27.05176496858137</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.5811190249794</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.31064404587264</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.47140263632917</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.14569739153401</v>
       </c>
     </row>
   </sheetData>
@@ -2632,19 +2632,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.50450561916379</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.80047849741233</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.49561282261273</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.37459745346946</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.10885587913317</v>
+        <v>33.43962365328814</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.76495446278468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.6685038803245</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.19843258267101</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.55170643882168</v>
       </c>
     </row>
   </sheetData>
@@ -2698,19 +2698,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.75047746717937</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.45003413292638</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49.69760881068721</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.82185103921122</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.25419792069776</v>
+        <v>30.77081221011936</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.85438555249959</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.95533048637945</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.29140985331105</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.96003666817351</v>
       </c>
     </row>
   </sheetData>
@@ -2764,19 +2764,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.43540719571428</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.01488030242753</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.44142039302528</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.95695191163276</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.57737727206857</v>
+        <v>33.50792482801211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.45364009776107</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.3563601118353</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.58420249776102</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.5118173012022</v>
       </c>
     </row>
   </sheetData>
@@ -2830,19 +2830,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.07588047161225</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.85070069364174</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.69833598765425</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.29876303612107</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.6418870387367</v>
+        <v>28.56389305707991</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.67776649879005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.25853315223651</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.44214192831419</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.76926018031128</v>
       </c>
     </row>
   </sheetData>
@@ -2896,19 +2896,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.77392081239014</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.56319639196418</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.98341849070466</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.76097289022512</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.36679342089241</v>
+        <v>30.22917253832888</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.97338751899758</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.24475712070194</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.7158877930146</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.25305446605568</v>
       </c>
     </row>
   </sheetData>
@@ -2962,19 +2962,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.45209820999215</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.37488071582424</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.28251746874967</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.61047325659339</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.02892659646745</v>
+        <v>25.32861958557434</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.98257467163773</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.97553805355</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.86864729761131</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.27630902775688</v>
       </c>
     </row>
   </sheetData>
@@ -3028,19 +3028,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.06588605925172</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.64424556636373</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.59381797315655</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.4706635126695</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.09452072229897</v>
+        <v>34.56074041840375</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.43545812160334</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.12679729063901</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.01814037219308</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.40285979895337</v>
       </c>
     </row>
   </sheetData>
@@ -3094,19 +3094,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.88148351795763</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.8953754163531</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.36540615856045</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40.82146517460109</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.14499195619941</v>
+        <v>26.66131893638372</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.56234123952659</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.01057168193034</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.85345105291771</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.09336788313017</v>
       </c>
     </row>
   </sheetData>
@@ -3160,19 +3160,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.02854660227506</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.76091976857447</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.52333932731652</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.49256594781807</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.63077671720315</v>
+        <v>34.1421171468832</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.03198134697049</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.11559646567006</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.2680514846106</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.95440959087844</v>
       </c>
     </row>
   </sheetData>
@@ -3226,19 +3226,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.11506017091188</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.57980550127615</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.6303339622695</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.79753314888347</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.34608521193997</v>
+        <v>27.17163700816582</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.45827087670315</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.90808562112526</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.72582427696231</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.39196256387962</v>
       </c>
     </row>
   </sheetData>
@@ -3292,19 +3292,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.3031365352388</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.11418164319755</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.83714810792202</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.25341821534396</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.59824520121226</v>
+        <v>33.88662722420078</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.29651703318387</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.56767271762695</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.51556092131882</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.35401621387817</v>
       </c>
     </row>
   </sheetData>
@@ -3358,19 +3358,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.9897966674707</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.04358826981594</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.25365552179493</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.91345502536863</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.82560109368553</v>
+        <v>32.92286217241112</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.70847522589001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.29663406640854</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.87380275289968</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.79157697239322</v>
       </c>
     </row>
   </sheetData>
@@ -3424,19 +3424,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.97795103241998</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.21229946341934</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.74262782900751</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.8719452086066</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.44528586414399</v>
+        <v>29.71908931548389</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.07617822091417</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.1508646501747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.84102918779333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.07431290774194</v>
       </c>
     </row>
   </sheetData>
@@ -3490,19 +3490,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.43883561145603</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.69454178213346</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.43767488842319</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.70024727330189</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.13302016536241</v>
+        <v>29.21882137426485</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.49246816949485</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.62704550137412</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.60139628343855</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.12878958296532</v>
       </c>
     </row>
   </sheetData>
@@ -3556,19 +3556,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.7142456242178</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.7879353125939</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.51465407092689</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.55082039905465</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.09364618543302</v>
+        <v>27.94823599796008</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.9715594602266</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.36021028444228</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.49569694785115</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.99212033315202</v>
       </c>
     </row>
   </sheetData>
@@ -3622,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.65456148618394</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.45866830461681</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.51692823530976</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.33571638369765</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.64152127675587</v>
+        <v>34.72031424451492</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.53228473250494</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.81736586702075</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.00611423597251</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.04717756655805</v>
       </c>
     </row>
   </sheetData>
@@ -3688,19 +3688,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.80532327317491</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.33116744193154</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.46278711073651</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.02428974027436</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.87108172812531</v>
+        <v>23.12935538676204</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.02871320992819</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.64401790635212</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.17006187088719</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.18092318826388</v>
       </c>
     </row>
   </sheetData>
@@ -3754,19 +3754,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.9539958134668</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.06963314222577</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.0520405369887</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.02420873086194</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.17117241978746</v>
+        <v>29.65002079469469</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.29462005567473</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.01820719748564</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.19112855237691</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.12068857196708</v>
       </c>
     </row>
   </sheetData>
@@ -3820,19 +3820,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.32398659071973</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.64341720708966</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.95528057608369</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.84917479766442</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.43846856242745</v>
+        <v>26.28560844241364</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.58775127200273</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.08013316311669</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.86881603352427</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.18518896204015</v>
       </c>
     </row>
   </sheetData>
@@ -3886,19 +3886,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.13843501266197</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.79179124414883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.82623624271899</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.88832089048758</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.65212053914004</v>
+        <v>25.68347911598297</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.75892938657308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.21435182620777</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.52398064661154</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.10605260247499</v>
       </c>
     </row>
   </sheetData>
@@ -3952,19 +3952,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.33012599597582</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.22511800037378</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.61960043098138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.48545719384851</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.82795232327095</v>
+        <v>32.46286767581228</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.07573486797218</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.48562636694035</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.58145026451548</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.2312813713193</v>
       </c>
     </row>
   </sheetData>
@@ -4018,19 +4018,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.25427345439717</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.72134987395661</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.63752009896266</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.33376190186342</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.0259680772911</v>
+        <v>30.53838416441527</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.80910548441876</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.5195019801228</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.07859741789723</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.90484591915757</v>
       </c>
     </row>
   </sheetData>
@@ -4084,19 +4084,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.63821456909435</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.41655817121639</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.64680185140125</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.48668215016749</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.49466338849242</v>
+        <v>23.30077978756985</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.45005523007464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.41785281533117</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.32740362545111</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.47308822345583</v>
       </c>
     </row>
   </sheetData>
@@ -4150,19 +4150,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.86323030914781</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.62628389489569</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.8774684285752</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.25708969846318</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.10107310901604</v>
+        <v>27.38987400022074</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.28407981289078</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.84807700056646</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.75179908468178</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.06119006493677</v>
       </c>
     </row>
   </sheetData>
@@ -4216,19 +4216,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.89051849807233</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.34010386529727</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.13151890966546</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.65050568071636</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.18519778483343</v>
+        <v>33.14315700240797</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.01809351462607</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.62072233531449</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.13855060379485</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.68529732471929</v>
       </c>
     </row>
   </sheetData>
@@ -4282,19 +4282,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.5066915740157</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.47995540651487</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.60275740493297</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.72682422054784</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.46253991918187</v>
+        <v>42.1489963646237</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.97690634041062</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.05949193216338</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.27117802873291</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.83533182610916</v>
       </c>
     </row>
   </sheetData>
@@ -4348,19 +4348,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.65374772162501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.39352854329111</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.17059257317185</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.61582703303149</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.92238726642377</v>
+        <v>28.08133769769971</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.86277949156284</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.1134861980237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.20300393819373</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.4229280621693</v>
       </c>
     </row>
   </sheetData>
@@ -4414,19 +4414,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.00206479308748</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.71769448934754</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.70539816919312</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.39585261993098</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.11183736778192</v>
+        <v>26.46591968245787</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.98966854661101</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.16472792923367</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.45077570537563</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.20262040360338</v>
       </c>
     </row>
   </sheetData>
@@ -4480,19 +4480,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.83892688662464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.60840688566696</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.55998919081144</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.49753680950426</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.84487588649575</v>
+        <v>24.38867827055748</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.63430219807467</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.15374610430476</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.70076122228892</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.17734639813632</v>
       </c>
     </row>
   </sheetData>
@@ -4546,19 +4546,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.86149246612003</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.00029744538717</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.95787156736886</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.01740225281955</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.77975139166436</v>
+        <v>40.32113799964638</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.09132898400462</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.69475037339254</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.50847395769608</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.9687519173697</v>
       </c>
     </row>
   </sheetData>
@@ -4612,19 +4612,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.95963812710579</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.23106181990177</v>
-      </c>
-      <c r="D2" t="n">
-        <v>43.9673346634751</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.74484551877137</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.05976897146031</v>
+        <v>28.14282834720818</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.14834716561595</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.78109872699451</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.20491545165485</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.29227930574971</v>
       </c>
     </row>
   </sheetData>
@@ -4678,19 +4678,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.32453427612277</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.81994351038504</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.67404384594707</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.37795057041542</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.31164521447462</v>
+        <v>35.20838468166612</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.43693075121681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.64488585833011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.89387208594396</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.9389413504371</v>
       </c>
     </row>
   </sheetData>
@@ -4744,19 +4744,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.27586520836632</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.39786968798014</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.84040678736266</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.5360303515892</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.91632378186101</v>
+        <v>25.10374071862637</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.72960431710698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.31383875773178</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.84774324943411</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.4897621598441</v>
       </c>
     </row>
   </sheetData>
@@ -4810,19 +4810,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.46747169642427</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.54866250283301</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.07373298841658</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.10070423699711</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.78947453249027</v>
+        <v>34.02569350037636</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.456611840252</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.950233915909</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.63837723486324</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.06740459532191</v>
       </c>
     </row>
   </sheetData>
@@ -4876,19 +4876,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.12625175527148</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.77851704037919</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.83122590489899</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.77848944728497</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.93437955214639</v>
+        <v>33.06373898009376</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.10674171481309</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.46465419092367</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.07397695730669</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.01801875822751</v>
       </c>
     </row>
   </sheetData>
@@ -4942,19 +4942,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.97526595975084</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.72739181896351</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.56886520284304</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.02270442277507</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.38617908668359</v>
+        <v>21.32797992128136</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.68664634887097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.95170196925317</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.33187070136835</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.29162713443611</v>
       </c>
     </row>
   </sheetData>
@@ -5008,19 +5008,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.00725996424806</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.53819114692693</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.22675047061189</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.69883153076145</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.80098121035824</v>
+        <v>29.19784677291819</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.56662317784147</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.30603419497393</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.0057966717663</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.26015501794479</v>
       </c>
     </row>
   </sheetData>
@@ -5074,19 +5074,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.40218806371194</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.42846456692097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.36118563465521</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.93683608410072</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.29241170262257</v>
+        <v>25.78966942645096</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.66338992959715</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.1676625636694</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.83457534817421</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.02224828091029</v>
       </c>
     </row>
   </sheetData>
@@ -5140,19 +5140,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.54097494544634</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.00527905666317</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.76796083898554</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.64926450365468</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.86174353803597</v>
+        <v>28.28754427316272</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.76834148100932</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.83238418709657</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.92250906292148</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.2439239264443</v>
       </c>
     </row>
   </sheetData>
@@ -5206,19 +5206,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.60259790081635</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.80642133871984</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.18413185542339</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.46357340636157</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.83994584523729</v>
+        <v>28.94965397672406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.11709756477614</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.17429912099818</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.69559029057541</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.94261487918056</v>
       </c>
     </row>
   </sheetData>
@@ -5272,19 +5272,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.74825938012981</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.64266568573341</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.84069993688949</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.33612180659032</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.73339636961993</v>
+        <v>27.98459334914028</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.37869948312724</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.42973807213494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.94594371788726</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.56896683885479</v>
       </c>
     </row>
   </sheetData>
@@ -5338,19 +5338,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.66496454616384</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.29457940551598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.72731453232373</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.48588649800081</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.803283211944</v>
+        <v>30.83172540180245</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.05211567662504</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.10159351250224</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.61069189583897</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.8622430972964</v>
       </c>
     </row>
   </sheetData>
@@ -5404,19 +5404,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.05095572054528</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.11082449038114</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.34201746028469</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.87879272298212</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.16238341110747</v>
+        <v>36.96153702108893</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.41636584031934</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.4564749116267</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.87248186238848</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.47540081865024</v>
       </c>
     </row>
   </sheetData>
@@ -5470,19 +5470,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.86240284909194</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.63158503354428</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.9116165273413</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.95932164054037</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.04671760676563</v>
+        <v>33.31478284428572</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.23372575329728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.6099831490572</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.08967127650363</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.1309599762155</v>
       </c>
     </row>
   </sheetData>
@@ -5536,19 +5536,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.82623651330645</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.84066281894367</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.82622270006132</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.24011952120172</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.81509114112348</v>
+        <v>25.87975901654659</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.45781066317496</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.25846035382392</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.36630466961883</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.02326213473885</v>
       </c>
     </row>
   </sheetData>
@@ -5602,19 +5602,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.49992717097561</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.24772700670891</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.06374691425964</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.59062382551702</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.50665997258869</v>
+        <v>44.17573911374306</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.64867691309706</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.35324837022191</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.44264978581878</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.81813342320823</v>
       </c>
     </row>
   </sheetData>
@@ -5668,19 +5668,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.86456990903147</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.9619820129722</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.69802156913398</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.88852812649442</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.00529545057674</v>
+        <v>35.69891985071664</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.04388706529219</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.93453526533662</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.07922774459521</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.46296710140958</v>
       </c>
     </row>
   </sheetData>
@@ -5734,19 +5734,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.87419170416372</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.5222072610351</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.98326889558829</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.99892284947193</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.12210139533154</v>
+        <v>29.79005763767966</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.63597576655204</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.3264999084147</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.38120055663815</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.06625911199455</v>
       </c>
     </row>
   </sheetData>
@@ -5800,19 +5800,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.91238903578017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.63029733725381</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.06983479196468</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.0498403157478</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.29095096318107</v>
+        <v>21.76160008909732</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.14744146707697</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.06113736074883</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.73004689122088</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.36162394880138</v>
       </c>
     </row>
   </sheetData>
@@ -5866,19 +5866,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.0095917659374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.48880844824018</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.35637364595449</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.24657901799952</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.40509055622242</v>
+        <v>38.60244828157625</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.35194492523048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.2951164377361</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.86363577579629</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20.29917706499846</v>
       </c>
     </row>
   </sheetData>
@@ -5932,19 +5932,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.63521794214221</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.46112727316476</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.58594564376058</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.53655847549951</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.80467627961981</v>
+        <v>34.49938208914001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.11743374175651</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.40010027015586</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.52305603207585</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.30719170819605</v>
       </c>
     </row>
   </sheetData>
@@ -5998,19 +5998,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.71058617893371</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.62636568970341</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.1094866456695</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.06249042881703</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.59022452418446</v>
+        <v>32.63267150756528</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.90154985391125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.57178238554818</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.62814998742496</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.19975637785123</v>
       </c>
     </row>
   </sheetData>
@@ -6064,19 +6064,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.38511065707021</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.88361560983336</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.8201321229559</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.9230697533303</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.52318013481413</v>
+        <v>38.14901988040845</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.82662328715151</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.72821765860141</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.37497787037912</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.90548835798498</v>
       </c>
     </row>
   </sheetData>
@@ -6130,19 +6130,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.52507667395884</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.78325244504233</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.93521170569193</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.65008363119774</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.77185947185437</v>
+        <v>26.45579222853298</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.29547057232765</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40.465264710645</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.10139039745409</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.20397026718474</v>
       </c>
     </row>
   </sheetData>
@@ -6196,19 +6196,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.01439984662839</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.87416045351132</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.79827857515506</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.25382924267624</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.91418652367885</v>
+        <v>28.54445644038644</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.68992983322143</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.46843627829655</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.41602199371922</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.59064721129739</v>
       </c>
     </row>
   </sheetData>
@@ -6262,19 +6262,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.49708049329933</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.24592232930208</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.42089897822162</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.29054824246715</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.66295203424434</v>
+        <v>25.46315307240907</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.79129701179518</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.88417423855977</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.55684390016513</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.13418311075717</v>
       </c>
     </row>
   </sheetData>
@@ -6328,19 +6328,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.65091599082793</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.80524732841717</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.65186531507128</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.35162168539258</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.86287420921366</v>
+        <v>18.16848124228592</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.69910187231473</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.68297652074742</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.46091077110831</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.84759741923629</v>
       </c>
     </row>
   </sheetData>
@@ -6394,19 +6394,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.70640302222657</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.69134030458831</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.54612705309136</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.16482311411379</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.50290966181355</v>
+        <v>27.85402088366497</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.1382511649749</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.18470059205861</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.07334656500144</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.86750002095046</v>
       </c>
     </row>
   </sheetData>
@@ -6460,19 +6460,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.45144748047011</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.79851319416689</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.76369949757435</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19.17206440275927</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.57126171130674</v>
+        <v>30.61655526928506</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.05799746988557</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.30704918605928</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.47567308876532</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.42487238343312</v>
       </c>
     </row>
   </sheetData>
@@ -6526,19 +6526,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.072794684622</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.16769258898196</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.16365306660342</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.55690730901998</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.327398951323</v>
+        <v>36.1537587533346</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.62603275208317</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.63113988263706</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.15384982223374</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.52804312915747</v>
       </c>
     </row>
   </sheetData>
@@ -6592,19 +6592,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.55344528213097</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.72909526611453</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.9055404163374</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.81108210033834</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.3260494949904</v>
+        <v>29.38676530887466</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.59549249550574</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.68245729621065</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.4866041228633</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.29232821023322</v>
       </c>
     </row>
   </sheetData>
@@ -6658,19 +6658,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.30532585604651</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.02774955214106</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.05025893265928</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.0498399390735</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.98350943442679</v>
+        <v>28.62028471513155</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.8866829824091</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.49914525784802</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.49967631161311</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.44933433459396</v>
       </c>
     </row>
   </sheetData>
@@ -6724,19 +6724,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.94537551243512</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.38119147815763</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.87754461058322</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.09382370311103</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.65970563891261</v>
+        <v>26.58706787022318</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.33961177558706</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.93620117691341</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.37518452989709</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.52325252310111</v>
       </c>
     </row>
   </sheetData>
@@ -6790,19 +6790,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.68199824648017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.43113585680446</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.93901388429514</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.11869415998169</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.76500933912944</v>
+        <v>35.89320950287818</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.60756149513677</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.05577937354617</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.61328153121374</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.52691855778196</v>
       </c>
     </row>
   </sheetData>
@@ -6856,19 +6856,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.82358642994867</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.83848869113139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.96200826308916</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.88363322542824</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.42766155326397</v>
+        <v>33.48814768631178</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.68885797390794</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.18154165014546</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.52903965034438</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.99538895543514</v>
       </c>
     </row>
   </sheetData>
@@ -6922,19 +6922,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.62442677147841</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.75605234047319</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.98226300510952</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.4585813829216</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.8945617818394</v>
+        <v>26.60921479338344</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.4931491965527</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.05161382097124</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.75451176751141</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.52513977954149</v>
       </c>
     </row>
   </sheetData>
@@ -6988,19 +6988,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.8958593692256</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.64482069342996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.86659255122026</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.37367156361076</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.12108632742987</v>
+        <v>36.68956780310565</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.97841533841445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.77363676612298</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.50023499098768</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.78869593156297</v>
       </c>
     </row>
   </sheetData>
@@ -7054,19 +7054,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.03726745004368</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.2837230100296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.73867152536005</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.79771907879474</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.34668086829772</v>
+        <v>35.28791125679137</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.48525356448097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.53096882276976</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.65561539103636</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.06294336636628</v>
       </c>
     </row>
   </sheetData>
@@ -7120,19 +7120,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.94667004529677</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.41064358174162</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.16011504956241</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.87220837083618</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.55078172089866</v>
+        <v>29.85255668018314</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.52027870689401</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.53928134577565</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.15561880338485</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.35227545239987</v>
       </c>
     </row>
   </sheetData>
@@ -7186,19 +7186,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.70003842144435</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.24758692587123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.89137875219801</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.02961108305082</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.1640714162125</v>
+        <v>22.6583370896542</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.04145411865863</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.57245847988423</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.1445535825259</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.19724225973677</v>
       </c>
     </row>
   </sheetData>
@@ -7252,19 +7252,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.26772406001759</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.28242977369681</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.09905321365238</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.34625388234475</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.00113637989695</v>
+        <v>37.79673872546292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.22215443890452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.35947196618751</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.69422498217314</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.43958014753988</v>
       </c>
     </row>
   </sheetData>
@@ -7318,19 +7318,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.51364476029456</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.44071151324598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.83126739839673</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.05408154724707</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.41138051804216</v>
+        <v>24.06187850707334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.05005565731738</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.77105855917897</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.74256977102264</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.07671423085328</v>
       </c>
     </row>
   </sheetData>
@@ -7384,19 +7384,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.47156422054519</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.39029014463177</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.14767854414479</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.97847912765328</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.61986342337215</v>
+        <v>31.84698998936686</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.34375273143458</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.21394896734786</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.28005471370082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.16950405555976</v>
       </c>
     </row>
   </sheetData>
@@ -7450,19 +7450,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.10052078205824</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.91855200879275</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.78829722924151</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.19636958348025</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.71543550353895</v>
+        <v>38.8250047509881</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.97119775172299</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.90825972945423</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.22789039744499</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.37514544439468</v>
       </c>
     </row>
   </sheetData>
@@ -7516,19 +7516,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.66214610069805</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.49600060147367</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.6346678964122</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.07374088561635</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.69330121862025</v>
+        <v>28.37798155038112</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.59331400782578</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.83939176310319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.66458824847679</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.1678837915679</v>
       </c>
     </row>
   </sheetData>
@@ -7582,19 +7582,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.9036256719623</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.0936324933771</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.20929563763544</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.78310728011336</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.82661282937661</v>
+        <v>30.30309008385466</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.0333914170037</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.34546732036145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51.2514681744473</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.63210979328375</v>
       </c>
     </row>
   </sheetData>
@@ -7648,19 +7648,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.39050949314058</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.25271069378542</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.07635479912514</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.33042199250412</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.98043672285542</v>
+        <v>31.0184662013736</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.71476024774596</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.53447970507808</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41.53760430056231</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.80894670038901</v>
       </c>
     </row>
   </sheetData>
@@ -7714,19 +7714,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.88313164281465</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.14983762198602</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.02909247775506</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.2436748911371</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.67217491591663</v>
+        <v>32.8956020155346</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.26839284855103</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.43514922007873</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.22791323407091</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.79729481069209</v>
       </c>
     </row>
   </sheetData>
@@ -7780,19 +7780,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.21851670721175</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.40753065903419</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.69560285019955</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.81833196239397</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.03000009831921</v>
+        <v>36.0874945922856</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.93870400746045</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.1805215550192</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.21829545152322</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.27558092809112</v>
       </c>
     </row>
   </sheetData>
@@ -7846,19 +7846,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.27649478450144</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.61532508628003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.69875857767287</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.63289597483563</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.72327456342768</v>
+        <v>29.33550917464886</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.24117286026469</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.555495068819</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.32071584647981</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.78359717396334</v>
       </c>
     </row>
   </sheetData>
@@ -7912,19 +7912,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.62676545924424</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.35224998045046</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.51561167975885</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.44706557237917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.53411777165695</v>
+        <v>35.24618101303838</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.91092774644423</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.25796402310461</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.86155118900492</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.00163565923415</v>
       </c>
     </row>
   </sheetData>
@@ -7978,19 +7978,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.88141831041497</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.42301547752309</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.57741915765828</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.5377730921551</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.03780173980492</v>
+        <v>34.3031618565382</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.79898931408096</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.34394332558662</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.29714751147711</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.99037020117119</v>
       </c>
     </row>
   </sheetData>
@@ -8044,19 +8044,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.95947089947687</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.11267263401859</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.84865790375054</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.65407996451638</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.77857658365746</v>
+        <v>28.46312848256695</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.23872563070601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.7163297858809</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.9014225466258</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.31046053767009</v>
       </c>
     </row>
   </sheetData>
@@ -8110,19 +8110,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.68542784177809</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.62788544643958</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.3448499552369</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.37773251837597</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.15511757309883</v>
+        <v>32.60526622163295</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.25874108097033</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.38167386666272</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.47488646762179</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.97638997183692</v>
       </c>
     </row>
   </sheetData>
@@ -8176,19 +8176,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.74383002224712</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.90602304018913</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.2234906222196</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.48879695681524</v>
-      </c>
-      <c r="F2" t="n">
-        <v>45.80212412921841</v>
+        <v>28.12879400997812</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.30305182858623</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.18412678241695</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.1402932440966</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.03946079394358</v>
       </c>
     </row>
   </sheetData>
@@ -8242,19 +8242,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.83835994869803</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.70234010743905</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.95359374016155</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.83171239437545</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.03234068924156</v>
+        <v>29.5247049987827</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.35059184126358</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.93497842972828</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38.81437934231475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.70765990714736</v>
       </c>
     </row>
   </sheetData>
@@ -8308,19 +8308,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.88809793048327</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.84923985850769</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.2406797536015</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.79992361471679</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.84152568972863</v>
+        <v>31.03439429030503</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.01312830445918</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.32488220249887</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.63406559958123</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.33769798700162</v>
       </c>
     </row>
   </sheetData>
@@ -8374,19 +8374,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.38140663962837</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.10563700798053</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.92504693880479</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.7518399427101</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.64494321272254</v>
+        <v>23.25714198526433</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.05927306204338</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.41305294311881</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.19805301780137</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20.24629660935086</v>
       </c>
     </row>
   </sheetData>
@@ -8440,19 +8440,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.98835355872604</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.31669005296727</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.1551637749799</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.74566758677237</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.91376320356973</v>
+        <v>24.87949308590869</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.34961317285192</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.39332963199174</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.28317860025863</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.81231161537468</v>
       </c>
     </row>
   </sheetData>
@@ -8506,19 +8506,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.38242211157035</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.81781839124585</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.77170076281965</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.18836156053292</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.67921536773778</v>
+        <v>42.19273437438746</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.16318277161358</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.79597847739463</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.24545441482793</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.82261508990877</v>
       </c>
     </row>
   </sheetData>
@@ -8572,19 +8572,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.66589874164701</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.42063026667786</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.81709860957265</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.7840181162231</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.68961940607325</v>
+        <v>25.18339282567506</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.75168746890251</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.02593606615627</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.88822126478231</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.79817836816521</v>
       </c>
     </row>
   </sheetData>
@@ -8638,19 +8638,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.95505754732012</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.11226097090587</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.1016401558418</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.0090973028262</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.93625097447877</v>
+        <v>29.95416178366497</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.89961374641298</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.52930821166088</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.15312050293861</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.03898243302013</v>
       </c>
     </row>
   </sheetData>
@@ -8704,19 +8704,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.94520179610299</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.72676256631632</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.89256979116592</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.21273473427143</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.26288226943142</v>
+        <v>23.25337958386311</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.14953169335964</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.92667182734872</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.67717130752534</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.64599623226696</v>
       </c>
     </row>
   </sheetData>
@@ -8770,19 +8770,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.04958528465016</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.25201978664446</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.49849277286727</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.75573449376554</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.13921071035283</v>
+        <v>26.54188229218742</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.98344547270985</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.38997410839051</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.66227224058527</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.58630796465926</v>
       </c>
     </row>
   </sheetData>
@@ -8836,19 +8836,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.04318694513761</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.4482362416984</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.33418968648861</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.67366339708724</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.82544009746232</v>
+        <v>34.61455614471515</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.39522725504943</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.42505661440473</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.67181039801661</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.33621157380524</v>
       </c>
     </row>
   </sheetData>
@@ -8902,19 +8902,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.68153644698738</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.82943770289224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.24887859201902</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.94473935372954</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.30346969861619</v>
+        <v>30.3704393358652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.31378353939755</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.8348827994616</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.33699894735491</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.82451433825038</v>
       </c>
     </row>
   </sheetData>
@@ -8968,19 +8968,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.94628836037108</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.25004576744393</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.2991657555467</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.80291736765432</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.53233614170586</v>
+        <v>28.42764471474114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.79463693409994</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.60068446933676</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.16529215404205</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.40699459674422</v>
       </c>
     </row>
   </sheetData>
@@ -9034,19 +9034,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.51934546717364</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.94943599869169</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.35893994431179</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.86117502189855</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.55183388285794</v>
+        <v>27.12789304612407</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.38468693113121</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.60634018905002</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.90100165423499</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.27979061455667</v>
       </c>
     </row>
   </sheetData>
@@ -9100,19 +9100,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.1197101768955</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.53013282649425</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.08437927546439</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.33241453423206</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.3605213481383</v>
+        <v>40.00171531724871</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.1037421035625</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.81369728599015</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.46428710142409</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.69409720162444</v>
       </c>
     </row>
   </sheetData>
@@ -9166,19 +9166,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.98955608650607</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.07550773435996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>40.65775896727298</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.52122365557428</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.76784699011561</v>
+        <v>36.90777950014191</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.43091442791221</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.02952421442904</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.85256917321973</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.49083042547129</v>
       </c>
     </row>
   </sheetData>
@@ -9232,19 +9232,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.59420158627666</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.4092735339947</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.14691567721577</v>
-      </c>
-      <c r="E2" t="n">
-        <v>45.43221919284426</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.8162892178773</v>
+        <v>32.31005270646742</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.90406856289085</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.13883596753237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.75598071053316</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.30340041484926</v>
       </c>
     </row>
   </sheetData>
@@ -9298,19 +9298,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.96129447025406</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.3306650751447</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.14013379211247</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.67507013473929</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.2852519762442</v>
+        <v>30.75945583816807</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.7300110514111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.29092520821895</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.75412128119323</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.18688688698867</v>
       </c>
     </row>
   </sheetData>
@@ -9364,19 +9364,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.67101530917776</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.0080574245945</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.10034399498831</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.59354206058752</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40.33714241837593</v>
+        <v>32.9361581828063</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.02908277813967</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.6685332272345</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.89463792285748</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.63044091465675</v>
       </c>
     </row>
   </sheetData>
@@ -9430,19 +9430,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.72609396125646</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.66707532900572</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.11965348299978</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.15536877004054</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.80152865905043</v>
+        <v>36.12710329030022</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.68521708160045</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.6765548795494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.91199445343931</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.68429925391904</v>
       </c>
     </row>
   </sheetData>
@@ -9496,19 +9496,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.18067178316423</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.19713554271659</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.5236858969096</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.04592133266244</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.74576535585203</v>
+        <v>30.05260591812479</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.53544313614269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.97593334339575</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.37182963430002</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.67773105448087</v>
       </c>
     </row>
   </sheetData>
@@ -9562,19 +9562,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.87941043693862</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.34939520432944</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.88844471600162</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.28455508107161</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.51816937427346</v>
+        <v>33.42590540379135</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.70979347107476</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42.66569648964502</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.91834309143952</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.67071140006083</v>
       </c>
     </row>
   </sheetData>
@@ -9628,19 +9628,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.84283843520728</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.32483212994746</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.73141678642322</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.16192690327117</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.59627209491778</v>
+        <v>25.98917107841167</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.53822813750933</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.0986696256516</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.30961415464676</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.08802757181906</v>
       </c>
     </row>
   </sheetData>
@@ -9694,19 +9694,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.17420428351965</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.71995622281027</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.18147871441527</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.86778122573964</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.8116113175853</v>
+        <v>31.49059346896604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.00059891428265</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.25724279626178</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.77020412063314</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.04537760427168</v>
       </c>
     </row>
   </sheetData>
@@ -9760,19 +9760,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.92737908100786</v>
-      </c>
-      <c r="C2" t="n">
-        <v>42.01357611526986</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.48166858310153</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.8440230133708</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.73905876427489</v>
+        <v>31.55939139627256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.17741390183398</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.4940422830147</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37.55967171480589</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.01319330483006</v>
       </c>
     </row>
   </sheetData>
@@ -9826,19 +9826,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.00871140239669</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.53646715245949</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.07306849294783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.09854496906276</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.43635727377253</v>
+        <v>43.10153215395206</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.8867357455011</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.42671069678089</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.81028744553027</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.07721659043929</v>
       </c>
     </row>
   </sheetData>
@@ -9892,19 +9892,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.47473649604268</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.17634390544414</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.10626170131463</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.59759186989402</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.62656487056228</v>
+        <v>27.71363503450076</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.84648453494642</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.80400901956979</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.7504603926155</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.23433500697006</v>
       </c>
     </row>
   </sheetData>
@@ -9958,19 +9958,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.7454136549006</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.20424233802201</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.3258349827237</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.33202335813059</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.22839854930796</v>
+        <v>25.97846125543355</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.12258924323588</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.7463338296535</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.1861225218486</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.83961225191339</v>
       </c>
     </row>
   </sheetData>
@@ -10024,19 +10024,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.05377258551948</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.25638625050119</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.1794549524295</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.82201787033025</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.55377932813228</v>
+        <v>29.30700324378496</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.26470103509592</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.83310497832076</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.51453210360575</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.15601818024114</v>
       </c>
     </row>
   </sheetData>
@@ -10090,19 +10090,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.95555560866153</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.6934548423657</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.20106454023748</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.56482324284314</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.00102362023964</v>
+        <v>32.8806247189834</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.27270430962777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.3171123774194</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.79172664652856</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.22817655517128</v>
       </c>
     </row>
   </sheetData>
@@ -10156,19 +10156,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.25170072533952</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.87819747669715</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.56265836911135</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.04240112088581</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.2947623360575</v>
+        <v>27.17685997123266</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.60212574230633</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.46478320904258</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.78412973164184</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.5597606483555</v>
       </c>
     </row>
   </sheetData>
@@ -10222,19 +10222,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.76403081015703</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.83933346683344</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.29144088464253</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.87264604398689</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.80181515245083</v>
+        <v>23.62238376847882</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.32133480110519</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.29928446351778</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.47222519666175</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.82104813680294</v>
       </c>
     </row>
   </sheetData>
@@ -10288,19 +10288,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.48045539077151</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.27002707035863</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.15130444747443</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.27856390641532</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.95907394507142</v>
+        <v>29.42308105766917</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.6157444633259</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.42161881000375</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.65581331722151</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.70050832225342</v>
       </c>
     </row>
   </sheetData>
@@ -10354,19 +10354,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.93430570099249</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.54220253272778</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.77280961026307</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.27991930112793</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.77549085175819</v>
+        <v>28.014846987032</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.34182154837978</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.1219258765708</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.30679655744419</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.00544213465275</v>
       </c>
     </row>
   </sheetData>
@@ -10420,19 +10420,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.66031443232461</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.44339070103882</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.66002942026575</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.02309769472518</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.70989518807076</v>
+        <v>32.16663220245355</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.83359811376059</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.74374129947857</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.28476749440785</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.86026588417189</v>
       </c>
     </row>
   </sheetData>
@@ -10486,19 +10486,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.86424651497875</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.33181638550843</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.70548382099436</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.24457620868379</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.17284381300847</v>
+        <v>27.15157038315742</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.04739817381042</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.72994061421092</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.35375660548812</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.66773766207711</v>
       </c>
     </row>
   </sheetData>
@@ -10552,19 +10552,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.12171472482889</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.49426002416989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.94765106815098</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50.33770825541466</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.2187152857272</v>
+        <v>39.79620588090924</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.64015302489006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.77999619120147</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.24963921640567</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.97650836149666</v>
       </c>
     </row>
   </sheetData>
@@ -10618,19 +10618,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.65258290390334</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.11668440374221</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.87074741773534</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.14265481779613</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.69677293804516</v>
+        <v>26.30443462718286</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.76949449505144</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.63936046862704</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.92094320038895</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.57990009385495</v>
       </c>
     </row>
   </sheetData>
@@ -10684,19 +10684,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.94187672089451</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.49263311590188</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.38319194016542</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.43578007176197</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.34377627433453</v>
+        <v>27.64678856821699</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.60058280229568</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.18093364541429</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.07599412266999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.71267040860242</v>
       </c>
     </row>
   </sheetData>
@@ -10750,19 +10750,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.79672684546412</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.99601023895871</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.20703998723747</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.78460701754653</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.51845654850944</v>
+        <v>27.6571456337398</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.50309958894476</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.17875433462817</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.90250289818587</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.92477936537849</v>
       </c>
     </row>
   </sheetData>
@@ -10816,19 +10816,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.52683180998303</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.11960804972414</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.56887323365008</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.39494107893316</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.5122396408343</v>
+        <v>32.28583137733987</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.33780115724662</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.69577107609656</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.20954740642355</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.33871584878424</v>
       </c>
     </row>
   </sheetData>
@@ -10882,19 +10882,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.75166015993333</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.49473049825345</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.92256123716979</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.69448756041159</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.78951848728192</v>
+        <v>39.17490989066297</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.25199169427798</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.59484126327698</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.04221650404345</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.63850521857272</v>
       </c>
     </row>
   </sheetData>
@@ -10948,19 +10948,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.57263724666275</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.53848010558598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.73933313770748</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.16230783646844</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.98856023897655</v>
+        <v>33.06965096545064</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.13758031238501</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.58630695484577</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.65676041072753</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.59441099405979</v>
       </c>
     </row>
   </sheetData>
@@ -11014,19 +11014,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.94192454224867</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.30219135137247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.44638217433681</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.49347075151941</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.39057795369924</v>
+        <v>32.51103906097149</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.68676118642909</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.91117468323466</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.22004131556887</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.34865743738649</v>
       </c>
     </row>
   </sheetData>
@@ -11080,19 +11080,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.01389592745106</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.33659329175341</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.37922049512445</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.79566937822612</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.53633518891028</v>
+        <v>30.27673767681678</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.70877701172731</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.05486068531371</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.85757266478369</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.69529339559145</v>
       </c>
     </row>
   </sheetData>
@@ -11146,19 +11146,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.87384467054859</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.98155242717306</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.42987056155772</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.40819743775996</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47.1044972679509</v>
+        <v>43.85608532812828</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.02977691417201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.33435472381574</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.18325275335195</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.09078400448342</v>
       </c>
     </row>
   </sheetData>
@@ -11212,19 +11212,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.26387866830468</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.53008340936613</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.51161742703863</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.2599144719084</v>
-      </c>
-      <c r="F2" t="n">
-        <v>37.87731235417368</v>
+        <v>28.93882948207121</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.84270999855831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.55425690423544</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.80986918092521</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30.92037838515459</v>
       </c>
     </row>
   </sheetData>
@@ -11278,19 +11278,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.44206086679669</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.27799601440021</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.52378147980352</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.85044352144461</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.76695045577598</v>
+        <v>26.38222742747537</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.3690397433678</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.81105653327233</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.68271734448594</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.73681708831216</v>
       </c>
     </row>
   </sheetData>
@@ -11344,19 +11344,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.2168152535969</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.24845167528348</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.02546300273507</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.69435480003517</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.68953983330308</v>
+        <v>34.11798900352379</v>
+      </c>
+      <c r="C2" t="n">
+        <v>44.52334237360947</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.29826846313104</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.06147901079293</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.62847527131659</v>
       </c>
     </row>
   </sheetData>
@@ -11410,19 +11410,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.37843277122349</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.48331275807935</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45.72182020029796</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.96372744716541</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.01938632895901</v>
+        <v>32.7514155678474</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.52554066618971</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.93943659265987</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.98561145377735</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49.66304205170444</v>
       </c>
     </row>
   </sheetData>
@@ -11476,19 +11476,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.50357779445359</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.34391359590963</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.26024420750376</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.56882357053047</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.37717413338052</v>
+        <v>35.74483833690218</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.17812791470309</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.84265125042506</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.78926366217993</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.41924367300299</v>
       </c>
     </row>
   </sheetData>
@@ -11542,19 +11542,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.72660782534061</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.86394277418993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.00728484499826</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.36833281734646</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.83202645437546</v>
+        <v>26.33154591930812</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.63629267245479</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.84782129183876</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.89737358929836</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.08770151005276</v>
       </c>
     </row>
   </sheetData>
@@ -11608,19 +11608,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.54357863834942</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46.16595160302063</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.18149014446881</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.38378302683818</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.97079619563879</v>
+        <v>29.32253634793744</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.1120291505277</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.59360210853798</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.27949009354474</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.22964002762827</v>
       </c>
     </row>
   </sheetData>
@@ -11674,19 +11674,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.52649199586127</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.59348637255855</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.39063120963664</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.9362700273616</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.12699550247288</v>
+        <v>29.57338779808017</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.07047074544198</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.82924544375804</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.77413249361507</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.7458325552284</v>
       </c>
     </row>
   </sheetData>
@@ -11740,19 +11740,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.14454878815928</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.49987203895307</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.08409353749072</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.95703265054077</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.83887039801733</v>
+        <v>31.00398267066292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.94385164023745</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.66135364590257</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.55761283610098</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.08258043882086</v>
       </c>
     </row>
   </sheetData>
@@ -11806,19 +11806,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.64481120751972</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.48959375768417</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.58850780574831</v>
-      </c>
-      <c r="E2" t="n">
-        <v>44.94734677415636</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.59726973515419</v>
+        <v>25.87713969602227</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.5194963782546</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.3533877925494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.48724392984658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.93355380112219</v>
       </c>
     </row>
   </sheetData>
@@ -11872,19 +11872,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.60651330084773</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.37178986527647</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.41660234199644</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.94041594954818</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.60718228028391</v>
+        <v>29.18054545685205</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.80406655706692</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.44462995473297</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.82513816921433</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.74444876868688</v>
       </c>
     </row>
   </sheetData>
@@ -11938,19 +11938,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.39255120116967</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.82034842764735</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.59064323713379</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.2126817776622</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.51083065153849</v>
+        <v>26.21949577269415</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.44032214300178</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.3100701638923</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.20567440762537</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.80905843673898</v>
       </c>
     </row>
   </sheetData>
@@ -12004,19 +12004,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.107261905713</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.82719896196611</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.70176161363161</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.3306795679367</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39.62469541662145</v>
+        <v>26.8455389352053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.69750443928827</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.52755461829941</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.5791647106187</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.87909161540401</v>
       </c>
     </row>
   </sheetData>
@@ -12070,19 +12070,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.64893413096174</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.56889269524778</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.273376717306</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.86858181965827</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.55130128082138</v>
+        <v>30.33083041777358</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.83921427508333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.82190752128141</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.8983559279111</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.95906800037995</v>
       </c>
     </row>
   </sheetData>
@@ -12136,19 +12136,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.34051041544591</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.2646716503068</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.02845163407894</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.1360912499329</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30.34778250364552</v>
+        <v>34.06468327949469</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.3664218375486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.73870735496286</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.00980104536565</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.64807296587892</v>
       </c>
     </row>
   </sheetData>
@@ -12202,19 +12202,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.52335792514109</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.27340927021788</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.06976089079097</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.92942348043138</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.92696875928641</v>
+        <v>25.07630004254918</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.40692532265833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.98544238270079</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.34562807313651</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.21909973422751</v>
       </c>
     </row>
   </sheetData>
@@ -12268,19 +12268,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.4911981568531</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.45433931853248</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.819861153326</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.35175960127386</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.41519596762301</v>
+        <v>33.20211840462591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.66721317120038</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.02417789799882</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.67656015769099</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.78075182775479</v>
       </c>
     </row>
   </sheetData>
@@ -12334,19 +12334,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.62677624311745</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.08743230692435</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.86582295214392</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.18988274708915</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.99587627049451</v>
+        <v>29.16420539945407</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.41929799767317</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.77428862470175</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.08347913115907</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.44821480564199</v>
       </c>
     </row>
   </sheetData>
@@ -12400,19 +12400,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.36887944073847</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.7395384532759</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.52261226282479</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.03931546251395</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.64781282902238</v>
+        <v>32.72119530159591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.74261529896186</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.84006788095122</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.57727870172688</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.40861065997854</v>
       </c>
     </row>
   </sheetData>
@@ -12466,19 +12466,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.35341419951138</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.97840503172016</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.62282671642852</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.15345556048936</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.25804392855428</v>
+        <v>34.97951690575145</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.08394464959621</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.59325883821703</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.81536349352746</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.27080968092449</v>
       </c>
     </row>
   </sheetData>
@@ -12532,19 +12532,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.99698887424793</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.31611412042138</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.27570360753173</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.03518831350998</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.51041553871115</v>
+        <v>35.25433877567541</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.78641067972806</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.06064485191541</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.16458475387058</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.51559907515649</v>
       </c>
     </row>
   </sheetData>
@@ -12598,19 +12598,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.66547701994264</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.42091376811975</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.88063865587248</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.64308211727305</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.00725429991738</v>
+        <v>35.17335845420745</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.48538216847564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.83365279300094</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.27143133622024</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.61845118157555</v>
       </c>
     </row>
   </sheetData>
@@ -12664,19 +12664,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.90886344332038</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.66580614128953</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.09283886574531</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.05781841582078</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27.49383259429552</v>
+        <v>30.7073156375072</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.54275908152007</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.5571272500232</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.6208100374518</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.77043544995002</v>
       </c>
     </row>
   </sheetData>
@@ -12730,19 +12730,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.93467869694505</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.16821952866997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.10344518419397</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.77954476100714</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.29862218515577</v>
+        <v>39.03351584187181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.25663167480636</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.31908665611493</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.53139428116303</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.10257625782118</v>
       </c>
     </row>
   </sheetData>
@@ -12796,19 +12796,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.24663918891241</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.66606768981803</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.75111541327037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.0935155409019</v>
-      </c>
-      <c r="F2" t="n">
-        <v>38.2942834277054</v>
+        <v>32.97526562825931</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.3012653788502</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.27658664340471</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.48720225085635</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.00678435914139</v>
       </c>
     </row>
   </sheetData>
@@ -12862,19 +12862,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.68641477923077</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.44384426415492</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.44889913177356</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.26921519507277</v>
-      </c>
-      <c r="F2" t="n">
-        <v>28.26583818904382</v>
+        <v>27.53829898106674</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.65535695299036</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.2957273438527</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.44993541939604</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.76162717635644</v>
       </c>
     </row>
   </sheetData>
@@ -12928,19 +12928,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.03871232971213</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.69352639281366</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.48186607466996</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.45529103684427</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.0304049345624</v>
+        <v>29.29113078934927</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38.33973917939112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.5133224743254</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.50216314872352</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.37705496784925</v>
       </c>
     </row>
   </sheetData>
@@ -12994,19 +12994,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.52788236218782</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.45360420106156</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.18158167078733</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.34502436463789</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.16440319745509</v>
+        <v>27.8788970538089</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.23991914579765</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.96615143178516</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.7124002672449</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.36986099555153</v>
       </c>
     </row>
   </sheetData>
@@ -13060,19 +13060,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.44746962566384</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.57755032127218</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.92799028266214</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.92236026619199</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36.77310946392198</v>
+        <v>37.14024830932885</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.33654468219972</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37.91504053962221</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.3452819606613</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.04449297795786</v>
       </c>
     </row>
   </sheetData>
@@ -13126,19 +13126,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.48193410214588</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.83124489527661</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.79361735491836</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.95112503003885</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32.21373926803165</v>
+        <v>38.40660690077615</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.93895106906037</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.43866674681536</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.6157608560425</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.5367677650456</v>
       </c>
     </row>
   </sheetData>
@@ -13192,19 +13192,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.70712846140271</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.9112037410443</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.7108871126932</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.21653386628595</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.63241103028308</v>
+        <v>26.72153610580353</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.45404375006345</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.77962752323833</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.05576960286032</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.99519199485495</v>
       </c>
     </row>
   </sheetData>
@@ -13258,19 +13258,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.43123933499658</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.97740325045025</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.11755627773092</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.96473404635786</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31.51142787611301</v>
+        <v>28.10840803106667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.90241820995589</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.08491377867598</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.19884827204</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.19385547678875</v>
       </c>
     </row>
   </sheetData>
@@ -13324,19 +13324,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.43953736479984</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.1225065238454</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18.88549432167813</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.36723237089722</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.27287927400152</v>
+        <v>28.019026441763</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.11929459589726</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.34709427327272</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.48195523090089</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.60307917643034</v>
       </c>
     </row>
   </sheetData>
@@ -13390,19 +13390,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.5487650689582</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.71852393551812</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.63632831371912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.41216761037523</v>
-      </c>
-      <c r="F2" t="n">
-        <v>35.82011549638439</v>
+        <v>29.97922063407701</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.62089863421161</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.30081459415108</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.09800056835658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.37197917361685</v>
       </c>
     </row>
   </sheetData>
@@ -13456,19 +13456,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.87234720423249</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.99287953721651</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.6915232520741</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.88897435383742</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.80159346853944</v>
+        <v>24.12176805018358</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.24484103504459</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.98202220295676</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.31047337112334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.49698490171829</v>
       </c>
     </row>
   </sheetData>
@@ -13522,19 +13522,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.34247755228782</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.49712534016155</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.34611466667748</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.62738591379949</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.49821781143044</v>
+        <v>26.06217210203958</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.20831832382127</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.11097798605256</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.11651775861491</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.62004027547019</v>
       </c>
     </row>
   </sheetData>
@@ -13588,19 +13588,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.26926733412599</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.71979575815134</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41.5851072762611</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.47284834792412</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.07617452602943</v>
+        <v>37.81299221077428</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.63675822829174</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.89477069394824</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.34865263984847</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.45775396774788</v>
       </c>
     </row>
   </sheetData>
@@ -13654,19 +13654,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.20709302831548</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.7508166790337</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.07515865875312</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.79053917179296</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29.69558079067473</v>
+        <v>28.93494619917561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.98175888706058</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.82271490220474</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.98619732919169</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26.34170471902229</v>
       </c>
     </row>
   </sheetData>
@@ -13720,19 +13720,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.21249128420522</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.39750380749179</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.83472364861987</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.10510696438019</v>
-      </c>
-      <c r="F2" t="n">
-        <v>34.11160936180518</v>
+        <v>30.24296149815411</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.21684869620092</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.32856083868111</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.70802127774896</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34.32335759576724</v>
       </c>
     </row>
   </sheetData>
@@ -13786,19 +13786,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.97546198069178</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.69108506056397</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.96305979986611</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.90166841706135</v>
-      </c>
-      <c r="F2" t="n">
-        <v>25.12295906260695</v>
+        <v>28.60366644887633</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.72979598516262</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.13895334406079</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.12095763076877</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.16904246386689</v>
       </c>
     </row>
   </sheetData>
